--- a/AMS/003-JeevanHeight/Jeevan_Heights_Provisional_BS_2025-26_V3.xlsx
+++ b/AMS/003-JeevanHeight/Jeevan_Heights_Provisional_BS_2025-26_V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\003-JeevanHeight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2297CC5A-2403-4B54-BF4B-1B30703856B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD640729-4F28-4457-AA59-B1D363A6951F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="797" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2448,7 +2448,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="347">
+  <cellXfs count="335">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2750,57 +2750,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2819,99 +2772,27 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1"/>
@@ -2926,9 +2807,6 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2938,9 +2816,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2953,36 +2828,12 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3040,30 +2891,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3072,15 +2905,6 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3102,9 +2926,6 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3144,9 +2965,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3157,15 +2975,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
@@ -3175,15 +2984,6 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3198,6 +2998,182 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3399,7 +3375,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57009DF9-DD51-4745-BD9F-B04A67D639D4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57009DF9-DD51-4745-BD9F-B04A67D639D4}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="X2:AC6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisCol" showAll="0" sumSubtotal="1">
@@ -3755,62 +3731,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="284" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="200"/>
+      <c r="B1" s="285"/>
+      <c r="C1" s="285"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="G1" s="285"/>
+      <c r="H1" s="286"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="294" t="s">
         <v>278</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="203"/>
+      <c r="B2" s="276"/>
+      <c r="C2" s="276"/>
+      <c r="D2" s="276"/>
+      <c r="E2" s="276"/>
+      <c r="F2" s="276"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="295"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="201" t="s">
+      <c r="A3" s="294" t="s">
         <v>268</v>
       </c>
-      <c r="B3" s="202"/>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="202"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="203"/>
+      <c r="B3" s="276"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
+      <c r="E3" s="276"/>
+      <c r="F3" s="276"/>
+      <c r="G3" s="276"/>
+      <c r="H3" s="295"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="204" t="s">
+      <c r="A4" s="291" t="s">
         <v>373</v>
       </c>
-      <c r="B4" s="205"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="206"/>
+      <c r="B4" s="292"/>
+      <c r="C4" s="292"/>
+      <c r="D4" s="292"/>
+      <c r="E4" s="292"/>
+      <c r="F4" s="292"/>
+      <c r="G4" s="292"/>
+      <c r="H4" s="293"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="177"/>
+      <c r="A5" s="161"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
-      <c r="H5" s="207" t="s">
+      <c r="H5" s="179" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3818,21 +3794,21 @@
       <c r="A6" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="B6" s="161" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="162"/>
-      <c r="D6" s="238" t="s">
+      <c r="B6" s="289" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="290"/>
+      <c r="D6" s="193" t="s">
         <v>374</v>
       </c>
-      <c r="E6" s="236" t="str">
+      <c r="E6" s="191" t="str">
         <f>A6</f>
         <v xml:space="preserve"> March 31, 2025</v>
       </c>
-      <c r="F6" s="161" t="s">
+      <c r="F6" s="289" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="162"/>
+      <c r="G6" s="290"/>
       <c r="H6" s="33" t="str">
         <f>D6</f>
         <v xml:space="preserve"> March 31, 2026</v>
@@ -3844,16 +3820,16 @@
         <v>85</v>
       </c>
       <c r="C7" s="31"/>
-      <c r="D7" s="239"/>
+      <c r="D7" s="194"/>
       <c r="E7" s="36"/>
-      <c r="F7" s="208" t="s">
+      <c r="F7" s="32" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="209">
+      <c r="A8" s="180">
         <f>4000*50</f>
         <v>200000</v>
       </c>
@@ -3861,7 +3837,7 @@
         <v>87</v>
       </c>
       <c r="C8" s="31"/>
-      <c r="D8" s="240">
+      <c r="D8" s="195">
         <v>200000</v>
       </c>
       <c r="E8" s="35">
@@ -3880,7 +3856,7 @@
       <c r="A9" s="8"/>
       <c r="B9" s="27"/>
       <c r="C9" s="31"/>
-      <c r="D9" s="239"/>
+      <c r="D9" s="194"/>
       <c r="E9" s="35">
         <f>BRS!A36</f>
         <v>54399</v>
@@ -3902,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="31"/>
-      <c r="D10" s="241">
+      <c r="D10" s="196">
         <v>31500</v>
       </c>
       <c r="E10" s="113">
@@ -3924,7 +3900,7 @@
         <v>88</v>
       </c>
       <c r="C11" s="31"/>
-      <c r="D11" s="239"/>
+      <c r="D11" s="194"/>
       <c r="E11" s="35">
         <f>BRS!A22</f>
         <v>55753.279999999999</v>
@@ -3945,9 +3921,8 @@
       <c r="A12" s="8"/>
       <c r="B12" s="27"/>
       <c r="C12" s="31"/>
-      <c r="D12" s="239"/>
+      <c r="D12" s="194"/>
       <c r="E12" s="36"/>
-      <c r="F12" s="210"/>
       <c r="G12" s="5"/>
       <c r="H12" s="7"/>
       <c r="J12" s="24"/>
@@ -3961,15 +3936,15 @@
         <v>224</v>
       </c>
       <c r="C13" s="31"/>
-      <c r="D13" s="239">
+      <c r="D13" s="196">
         <f>+'Sch 5'!E32</f>
-        <v>4575563.09</v>
+        <v>4720618.09</v>
       </c>
       <c r="E13" s="35">
         <f>4604276</f>
         <v>4604276</v>
       </c>
-      <c r="F13" s="208" t="s">
+      <c r="F13" s="32" t="s">
         <v>218</v>
       </c>
       <c r="G13" s="5"/>
@@ -3982,7 +3957,7 @@
       <c r="A14" s="8"/>
       <c r="B14" s="28"/>
       <c r="C14" s="31"/>
-      <c r="D14" s="239"/>
+      <c r="D14" s="194"/>
       <c r="E14" s="23"/>
       <c r="F14" s="38"/>
       <c r="G14" s="5"/>
@@ -3994,7 +3969,7 @@
         <v>225</v>
       </c>
       <c r="C15" s="31"/>
-      <c r="D15" s="239"/>
+      <c r="D15" s="194"/>
       <c r="E15" s="23"/>
       <c r="F15" s="39" t="s">
         <v>92</v>
@@ -4014,7 +3989,7 @@
         <f>'Sch 4,6'!D32</f>
         <v>299406</v>
       </c>
-      <c r="D16" s="239"/>
+      <c r="D16" s="194"/>
       <c r="E16" s="23">
         <f>'Sch 4,6'!B54</f>
         <v>20433</v>
@@ -4043,7 +4018,7 @@
         <f>+'Sch 4,6'!D39</f>
         <v>173317</v>
       </c>
-      <c r="D17" s="239"/>
+      <c r="D17" s="194"/>
       <c r="E17" s="26"/>
       <c r="F17" s="40"/>
       <c r="G17" s="5"/>
@@ -4061,7 +4036,7 @@
         <f>+'Sch 4,6'!D47</f>
         <v>126019</v>
       </c>
-      <c r="D18" s="239">
+      <c r="D18" s="194">
         <f>SUM(C16:C18)</f>
         <v>598742</v>
       </c>
@@ -4076,7 +4051,7 @@
       <c r="A19" s="7"/>
       <c r="B19" s="35"/>
       <c r="C19" s="31"/>
-      <c r="D19" s="239"/>
+      <c r="D19" s="194"/>
       <c r="E19" s="23">
         <f>73765+18798</f>
         <v>92563</v>
@@ -4096,7 +4071,7 @@
         <v>89</v>
       </c>
       <c r="C20" s="31"/>
-      <c r="D20" s="239"/>
+      <c r="D20" s="194"/>
       <c r="E20" s="23">
         <v>2721</v>
       </c>
@@ -4119,7 +4094,7 @@
         <v>226</v>
       </c>
       <c r="C21" s="31"/>
-      <c r="D21" s="239">
+      <c r="D21" s="194">
         <f>'Sch 3&amp;7'!D24</f>
         <v>112181</v>
       </c>
@@ -4132,7 +4107,7 @@
       <c r="A22" s="8"/>
       <c r="B22" s="29"/>
       <c r="C22" s="31"/>
-      <c r="D22" s="239"/>
+      <c r="D22" s="194"/>
       <c r="E22" s="26">
         <f>'Sch 2'!C15</f>
         <v>533313</v>
@@ -4152,7 +4127,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="31"/>
-      <c r="D23" s="239"/>
+      <c r="D23" s="194"/>
       <c r="E23" s="23"/>
       <c r="F23" s="40"/>
       <c r="G23" s="5"/>
@@ -4169,7 +4144,7 @@
         <f>1770482.23</f>
         <v>1770482.23</v>
       </c>
-      <c r="D24" s="239"/>
+      <c r="D24" s="194"/>
       <c r="E24" s="23"/>
       <c r="F24" s="4" t="s">
         <v>6</v>
@@ -4187,7 +4162,7 @@
       <c r="C25" s="31">
         <v>0</v>
       </c>
-      <c r="D25" s="239"/>
+      <c r="D25" s="194"/>
       <c r="E25" s="23">
         <v>65424</v>
       </c>
@@ -4210,11 +4185,11 @@
       </c>
       <c r="C26" s="6">
         <f>+PL!D46</f>
-        <v>548593</v>
-      </c>
-      <c r="D26" s="239">
+        <v>403538</v>
+      </c>
+      <c r="D26" s="194">
         <f>SUM(C24:C26)</f>
-        <v>2319075.23</v>
+        <v>2174020.23</v>
       </c>
       <c r="E26" s="23">
         <v>22033</v>
@@ -4231,7 +4206,7 @@
       <c r="A27" s="7"/>
       <c r="B27" s="36"/>
       <c r="C27" s="31"/>
-      <c r="D27" s="239"/>
+      <c r="D27" s="194"/>
       <c r="E27" s="23">
         <v>550</v>
       </c>
@@ -4247,7 +4222,7 @@
       <c r="A28" s="8"/>
       <c r="B28" s="29"/>
       <c r="C28" s="31"/>
-      <c r="D28" s="239"/>
+      <c r="D28" s="194"/>
       <c r="E28" s="23">
         <v>26115</v>
       </c>
@@ -4264,7 +4239,7 @@
       <c r="A29" s="8"/>
       <c r="B29" s="29"/>
       <c r="C29" s="31"/>
-      <c r="D29" s="239"/>
+      <c r="D29" s="194"/>
       <c r="E29" s="23">
         <v>53000</v>
       </c>
@@ -4285,7 +4260,7 @@
       <c r="A30" s="8"/>
       <c r="B30" s="29"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="239"/>
+      <c r="D30" s="194"/>
       <c r="E30" s="26"/>
       <c r="F30" s="40"/>
       <c r="G30" s="5"/>
@@ -4295,7 +4270,7 @@
       <c r="A31" s="8"/>
       <c r="B31" s="29"/>
       <c r="C31" s="31"/>
-      <c r="D31" s="239"/>
+      <c r="D31" s="194"/>
       <c r="E31" s="23">
         <f>+'Sch 4,6'!B13</f>
         <v>107878</v>
@@ -4314,46 +4289,44 @@
       <c r="A32" s="8"/>
       <c r="B32" s="29"/>
       <c r="C32" s="31"/>
-      <c r="D32" s="242"/>
+      <c r="D32" s="197"/>
       <c r="E32" s="26"/>
       <c r="F32" s="40"/>
       <c r="G32" s="5"/>
       <c r="H32" s="36"/>
     </row>
     <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="216">
+      <c r="A33" s="181">
         <f>SUM(A10:A32)</f>
         <v>6562190.3199999994</v>
       </c>
-      <c r="B33" s="217" t="s">
+      <c r="B33" s="287" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="218"/>
-      <c r="D33" s="243">
+      <c r="C33" s="288"/>
+      <c r="D33" s="198">
         <f>SUM(D10:D32)</f>
         <v>7637061.3200000003</v>
       </c>
-      <c r="E33" s="237">
+      <c r="E33" s="192">
         <f>SUM(E7:E32)</f>
         <v>6562190.3200000003</v>
       </c>
-      <c r="F33" s="218" t="s">
+      <c r="F33" s="288" t="s">
         <v>9</v>
       </c>
-      <c r="G33" s="218"/>
-      <c r="H33" s="216">
+      <c r="G33" s="288"/>
+      <c r="H33" s="181">
         <f>SUM(H7:H32)</f>
         <v>7637061.3200000003</v>
       </c>
       <c r="J33" s="135"/>
     </row>
     <row r="34" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="177"/>
-      <c r="B34" s="210"/>
+      <c r="A34" s="161"/>
       <c r="C34" s="31"/>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
-      <c r="F34" s="210"/>
       <c r="G34" s="31">
         <f>A33-E33</f>
         <v>0</v>
@@ -4364,122 +4337,103 @@
       </c>
       <c r="J34" s="135"/>
     </row>
-    <row r="35" spans="1:13" s="183" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="178" t="s">
+    <row r="35" spans="1:13" s="166" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A35" s="162" t="s">
         <v>495</v>
       </c>
-      <c r="B35" s="211"/>
-      <c r="C35" s="180"/>
-      <c r="D35" s="211"/>
-      <c r="E35" s="212" t="s">
+      <c r="B35" s="163"/>
+      <c r="C35" s="164"/>
+      <c r="D35" s="163"/>
+      <c r="E35" s="280" t="s">
         <v>496</v>
       </c>
-      <c r="F35" s="212"/>
-      <c r="G35" s="212"/>
-      <c r="H35" s="181"/>
-      <c r="I35" s="180"/>
-      <c r="J35" s="179"/>
-      <c r="K35" s="179"/>
-      <c r="L35" s="182"/>
-      <c r="M35" s="182"/>
-    </row>
-    <row r="36" spans="1:13" s="179" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A36" s="184"/>
-      <c r="B36" s="211"/>
-      <c r="C36" s="180"/>
-      <c r="D36" s="211"/>
-      <c r="E36" s="211"/>
-      <c r="F36" s="211"/>
-      <c r="G36" s="211"/>
-      <c r="H36" s="185"/>
-      <c r="I36" s="180"/>
-    </row>
-    <row r="37" spans="1:13" s="179" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A37" s="184"/>
-      <c r="B37" s="211"/>
-      <c r="C37" s="180"/>
-      <c r="D37" s="211"/>
-      <c r="E37" s="211"/>
-      <c r="F37" s="186"/>
-      <c r="G37" s="186"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="180"/>
-    </row>
-    <row r="38" spans="1:13" s="179" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="184"/>
-      <c r="B38" s="211"/>
-      <c r="C38" s="180"/>
-      <c r="D38" s="211"/>
-      <c r="E38" s="211"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="186"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="180"/>
-    </row>
-    <row r="39" spans="1:13" s="179" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="188" t="s">
+      <c r="F35" s="280"/>
+      <c r="G35" s="280"/>
+      <c r="H35" s="281"/>
+      <c r="I35" s="164"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="165"/>
+      <c r="M35" s="165"/>
+    </row>
+    <row r="36" spans="1:13" s="163" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A36" s="167"/>
+      <c r="C36" s="164"/>
+      <c r="H36" s="168"/>
+      <c r="I36" s="164"/>
+    </row>
+    <row r="37" spans="1:13" s="163" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A37" s="167"/>
+      <c r="C37" s="164"/>
+      <c r="F37" s="169"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="170"/>
+      <c r="I37" s="164"/>
+    </row>
+    <row r="38" spans="1:13" s="163" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A38" s="167"/>
+      <c r="C38" s="164"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="170"/>
+      <c r="I38" s="164"/>
+    </row>
+    <row r="39" spans="1:13" s="163" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="171" t="s">
         <v>497</v>
       </c>
-      <c r="B39" s="213"/>
-      <c r="C39" s="214"/>
-      <c r="D39" s="211"/>
-      <c r="E39" s="211"/>
-      <c r="F39" s="186"/>
-      <c r="G39" s="186"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="180"/>
-    </row>
-    <row r="40" spans="1:13" s="179" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="191" t="s">
+      <c r="B39" s="172"/>
+      <c r="C39" s="173"/>
+      <c r="F39" s="169"/>
+      <c r="G39" s="169"/>
+      <c r="H39" s="170"/>
+      <c r="I39" s="164"/>
+    </row>
+    <row r="40" spans="1:13" s="163" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A40" s="174" t="s">
         <v>498</v>
       </c>
-      <c r="B40" s="213"/>
-      <c r="C40" s="214"/>
-      <c r="D40" s="211"/>
-      <c r="E40" s="212" t="s">
+      <c r="B40" s="172"/>
+      <c r="C40" s="173"/>
+      <c r="E40" s="280" t="s">
         <v>499</v>
       </c>
-      <c r="F40" s="212"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="181"/>
-      <c r="I40" s="180"/>
-    </row>
-    <row r="41" spans="1:13" s="179" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="191" t="s">
+      <c r="F40" s="280"/>
+      <c r="G40" s="280"/>
+      <c r="H40" s="281"/>
+      <c r="I40" s="164"/>
+    </row>
+    <row r="41" spans="1:13" s="163" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A41" s="174" t="s">
         <v>500</v>
       </c>
-      <c r="B41" s="213"/>
-      <c r="C41" s="214"/>
-      <c r="D41" s="211"/>
-      <c r="E41" s="186"/>
-      <c r="F41" s="186"/>
-      <c r="G41" s="186"/>
-      <c r="H41" s="187"/>
-      <c r="I41" s="180"/>
-    </row>
-    <row r="42" spans="1:13" s="179" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A42" s="192">
-        <v>46221</v>
-      </c>
-      <c r="B42" s="215"/>
-      <c r="C42" s="215"/>
-      <c r="D42" s="211"/>
-      <c r="E42" s="211"/>
-      <c r="F42" s="211"/>
-      <c r="G42" s="211"/>
-      <c r="H42" s="185"/>
-      <c r="I42" s="180"/>
-    </row>
-    <row r="43" spans="1:13" s="179" customFormat="1" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="194"/>
-      <c r="B43" s="195"/>
-      <c r="C43" s="196"/>
-      <c r="D43" s="195"/>
-      <c r="E43" s="196"/>
-      <c r="F43" s="195"/>
-      <c r="G43" s="195"/>
-      <c r="H43" s="197"/>
-      <c r="I43" s="180"/>
+      <c r="B41" s="172"/>
+      <c r="C41" s="173"/>
+      <c r="E41" s="169"/>
+      <c r="F41" s="169"/>
+      <c r="G41" s="169"/>
+      <c r="H41" s="170"/>
+      <c r="I41" s="164"/>
+    </row>
+    <row r="42" spans="1:13" s="163" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A42" s="282">
+        <v>46229</v>
+      </c>
+      <c r="B42" s="283"/>
+      <c r="C42" s="283"/>
+      <c r="H42" s="168"/>
+      <c r="I42" s="164"/>
+    </row>
+    <row r="43" spans="1:13" s="163" customFormat="1" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="175"/>
+      <c r="B43" s="176"/>
+      <c r="C43" s="177"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="177"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="178"/>
+      <c r="I43" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4543,15 +4497,15 @@
       <c r="D2" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="166" t="s">
+      <c r="G2" s="302" t="s">
         <v>214</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
+      <c r="H2" s="302"/>
+      <c r="I2" s="302"/>
+      <c r="J2" s="302"/>
+      <c r="K2" s="302"/>
+      <c r="L2" s="302"/>
+      <c r="M2" s="302"/>
       <c r="N2" s="71" t="s">
         <v>438</v>
       </c>
@@ -6975,54 +6929,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="284" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="200"/>
+      <c r="B1" s="285"/>
+      <c r="C1" s="285"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="G1" s="285"/>
+      <c r="H1" s="286"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="221" t="str">
+      <c r="A2" s="298" t="str">
         <f>BS!A2</f>
         <v>Society Address: Bandar, Pakhadi Road  ,Kandivali (W), Mumbai - 400067.</v>
       </c>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="222"/>
-      <c r="F2" s="222"/>
-      <c r="G2" s="222"/>
-      <c r="H2" s="223"/>
+      <c r="B2" s="299"/>
+      <c r="C2" s="299"/>
+      <c r="D2" s="299"/>
+      <c r="E2" s="299"/>
+      <c r="F2" s="299"/>
+      <c r="G2" s="299"/>
+      <c r="H2" s="300"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="221" t="s">
+      <c r="A3" s="298" t="s">
         <v>268</v>
       </c>
-      <c r="B3" s="222"/>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
-      <c r="G3" s="222"/>
-      <c r="H3" s="223"/>
+      <c r="B3" s="299"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="299"/>
+      <c r="G3" s="299"/>
+      <c r="H3" s="300"/>
     </row>
     <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="204" t="s">
+      <c r="A4" s="291" t="s">
         <v>384</v>
       </c>
-      <c r="B4" s="205"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="206"/>
+      <c r="B4" s="292"/>
+      <c r="C4" s="292"/>
+      <c r="D4" s="292"/>
+      <c r="E4" s="292"/>
+      <c r="F4" s="292"/>
+      <c r="G4" s="292"/>
+      <c r="H4" s="293"/>
       <c r="M4" s="3" t="s">
         <v>164</v>
       </c>
@@ -7037,14 +6991,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="224"/>
-      <c r="B5" s="225"/>
-      <c r="C5" s="225"/>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="226" t="s">
+      <c r="A5" s="185"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="179" t="s">
         <v>84</v>
       </c>
       <c r="M5" s="14" t="s">
@@ -7055,34 +7009,34 @@
       </c>
       <c r="O5" s="60">
         <f>D9+D21+D29-C24-C26+D43-C43</f>
-        <v>3134026</v>
+        <v>3327433</v>
       </c>
       <c r="P5" s="59">
         <f>N5-O5</f>
-        <v>441854</v>
+        <v>248447</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="32" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="235" t="str">
+      <c r="A6" s="190" t="str">
         <f>BS!A6</f>
         <v xml:space="preserve"> March 31, 2025</v>
       </c>
-      <c r="B6" s="162" t="s">
+      <c r="B6" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="162"/>
-      <c r="D6" s="246" t="str">
+      <c r="C6" s="290"/>
+      <c r="D6" s="201" t="str">
         <f>BS!D6</f>
         <v xml:space="preserve"> March 31, 2026</v>
       </c>
-      <c r="E6" s="244" t="str">
+      <c r="E6" s="199" t="str">
         <f>A6</f>
         <v xml:space="preserve"> March 31, 2025</v>
       </c>
-      <c r="F6" s="162" t="s">
+      <c r="F6" s="290" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="162"/>
+      <c r="G6" s="290"/>
       <c r="H6" s="121" t="str">
         <f>D6</f>
         <v xml:space="preserve"> March 31, 2026</v>
@@ -7103,18 +7057,18 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="227"/>
+      <c r="A7" s="187"/>
       <c r="B7" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C7" s="113"/>
-      <c r="D7" s="247"/>
+      <c r="D7" s="202"/>
       <c r="E7" s="114"/>
       <c r="F7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="34"/>
-      <c r="H7" s="228"/>
+      <c r="H7" s="188"/>
       <c r="M7" s="14" t="s">
         <v>14</v>
       </c>
@@ -7131,7 +7085,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="227">
+      <c r="A8" s="187">
         <v>166200</v>
       </c>
       <c r="B8" s="34" t="s">
@@ -7141,7 +7095,7 @@
         <f>243250</f>
         <v>243250</v>
       </c>
-      <c r="D8" s="247"/>
+      <c r="D8" s="202"/>
       <c r="E8" s="114">
         <v>3575880</v>
       </c>
@@ -7151,7 +7105,7 @@
       <c r="G8" s="34">
         <v>3575880</v>
       </c>
-      <c r="H8" s="228"/>
+      <c r="H8" s="188"/>
       <c r="M8" s="14" t="s">
         <v>265</v>
       </c>
@@ -7168,7 +7122,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="227">
+      <c r="A9" s="187">
         <v>49600</v>
       </c>
       <c r="B9" s="34" t="s">
@@ -7178,20 +7132,20 @@
         <f>2500+47000</f>
         <v>49500</v>
       </c>
-      <c r="D9" s="247">
+      <c r="D9" s="202">
         <f>SUM(C8:C9)</f>
         <v>292750</v>
       </c>
       <c r="E9" s="114">
         <v>1388772</v>
       </c>
-      <c r="F9" s="229" t="s">
+      <c r="F9" s="40" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="34">
         <v>1388772</v>
       </c>
-      <c r="H9" s="228"/>
+      <c r="H9" s="188"/>
       <c r="M9" s="14" t="s">
         <v>124</v>
       </c>
@@ -7208,12 +7162,12 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="227"/>
+      <c r="A10" s="187"/>
       <c r="B10" s="39" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="113"/>
-      <c r="D10" s="247"/>
+      <c r="D10" s="202"/>
       <c r="E10" s="114">
         <v>401940</v>
       </c>
@@ -7223,7 +7177,7 @@
       <c r="G10" s="34">
         <v>401940</v>
       </c>
-      <c r="H10" s="228"/>
+      <c r="H10" s="188"/>
       <c r="M10" s="14" t="s">
         <v>125</v>
       </c>
@@ -7240,14 +7194,14 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="227">
+      <c r="A11" s="187">
         <v>111260</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="34"/>
-      <c r="D11" s="247">
+      <c r="D11" s="202">
         <f>130988</f>
         <v>130988</v>
       </c>
@@ -7261,7 +7215,7 @@
         <f>47280</f>
         <v>47280</v>
       </c>
-      <c r="H11" s="228"/>
+      <c r="H11" s="188"/>
       <c r="M11" s="14" t="s">
         <v>113</v>
       </c>
@@ -7278,12 +7232,12 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="227"/>
+      <c r="A12" s="187"/>
       <c r="B12" s="39" t="s">
         <v>104</v>
       </c>
       <c r="C12" s="113"/>
-      <c r="D12" s="247"/>
+      <c r="D12" s="202"/>
       <c r="E12" s="114">
         <v>84952</v>
       </c>
@@ -7293,7 +7247,7 @@
       <c r="G12" s="34">
         <v>84952</v>
       </c>
-      <c r="H12" s="228"/>
+      <c r="H12" s="188"/>
       <c r="M12" s="14" t="s">
         <v>267</v>
       </c>
@@ -7309,7 +7263,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="227">
+      <c r="A13" s="187">
         <f>1595680</f>
         <v>1595680</v>
       </c>
@@ -7317,7 +7271,7 @@
         <v>105</v>
       </c>
       <c r="C13" s="34"/>
-      <c r="D13" s="247">
+      <c r="D13" s="202">
         <f>1702520</f>
         <v>1702520</v>
       </c>
@@ -7330,7 +7284,7 @@
       <c r="G13" s="34">
         <v>226800</v>
       </c>
-      <c r="H13" s="228"/>
+      <c r="H13" s="188"/>
       <c r="M13" s="3" t="s">
         <v>270</v>
       </c>
@@ -7340,20 +7294,20 @@
       </c>
       <c r="O13" s="59">
         <f t="shared" ref="O13" si="1">SUM(O5:O12)</f>
-        <v>6148645</v>
+        <v>6342052</v>
       </c>
       <c r="P13" s="59">
         <f>SUM(P5:P12)</f>
-        <v>539727</v>
+        <v>346320</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="227"/>
+      <c r="A14" s="187"/>
       <c r="B14" s="39" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="113"/>
-      <c r="D14" s="247"/>
+      <c r="D14" s="202"/>
       <c r="E14" s="114">
         <v>24207</v>
       </c>
@@ -7364,7 +7318,7 @@
         <f>29466</f>
         <v>29466</v>
       </c>
-      <c r="H14" s="228">
+      <c r="H14" s="188">
         <f>SUM(G8:G14)</f>
         <v>5755090</v>
       </c>
@@ -7383,7 +7337,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="227">
+      <c r="A15" s="187">
         <f>186810</f>
         <v>186810</v>
       </c>
@@ -7394,11 +7348,11 @@
         <f>Workings!D9</f>
         <v>140421</v>
       </c>
-      <c r="D15" s="247"/>
+      <c r="D15" s="202"/>
       <c r="E15" s="114"/>
-      <c r="F15" s="229"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="34"/>
-      <c r="H15" s="228"/>
+      <c r="H15" s="188"/>
       <c r="M15" s="14" t="s">
         <v>266</v>
       </c>
@@ -7414,7 +7368,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="227">
+      <c r="A16" s="187">
         <f>47000-20000</f>
         <v>27000</v>
       </c>
@@ -7425,7 +7379,7 @@
         <f>7500</f>
         <v>7500</v>
       </c>
-      <c r="D16" s="247">
+      <c r="D16" s="202">
         <f>SUM(C15:C16)</f>
         <v>147921</v>
       </c>
@@ -7434,7 +7388,7 @@
         <v>102</v>
       </c>
       <c r="G16" s="34"/>
-      <c r="H16" s="228"/>
+      <c r="H16" s="188"/>
       <c r="M16" s="14" t="s">
         <v>126</v>
       </c>
@@ -7450,12 +7404,12 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="227"/>
+      <c r="A17" s="187"/>
       <c r="B17" s="39" t="s">
         <v>108</v>
       </c>
       <c r="C17" s="113"/>
-      <c r="D17" s="247"/>
+      <c r="D17" s="202"/>
       <c r="E17" s="114">
         <v>47628</v>
       </c>
@@ -7466,7 +7420,7 @@
         <f>3591+58401</f>
         <v>61992</v>
       </c>
-      <c r="H17" s="228"/>
+      <c r="H17" s="188"/>
       <c r="M17" s="14" t="s">
         <v>17</v>
       </c>
@@ -7482,7 +7436,7 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="227">
+      <c r="A18" s="187">
         <f>656445</f>
         <v>656445</v>
       </c>
@@ -7493,7 +7447,7 @@
         <f>Workings!D61</f>
         <v>698739</v>
       </c>
-      <c r="D18" s="247"/>
+      <c r="D18" s="202"/>
       <c r="E18" s="114">
         <v>65412</v>
       </c>
@@ -7504,7 +7458,7 @@
         <f>948+68256</f>
         <v>69204</v>
       </c>
-      <c r="H18" s="228">
+      <c r="H18" s="188">
         <f>SUM(G17:G18)</f>
         <v>131196</v>
       </c>
@@ -7523,7 +7477,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="227">
+      <c r="A19" s="187">
         <f>-A18</f>
         <v>-656445</v>
       </c>
@@ -7534,14 +7488,14 @@
         <f>-C18</f>
         <v>-698739</v>
       </c>
-      <c r="D19" s="247">
+      <c r="D19" s="202">
         <f>SUM(C18:C19)</f>
         <v>0</v>
       </c>
       <c r="E19" s="114"/>
-      <c r="F19" s="229"/>
+      <c r="F19" s="40"/>
       <c r="G19" s="34"/>
-      <c r="H19" s="228"/>
+      <c r="H19" s="188"/>
       <c r="M19" s="14" t="s">
         <v>20</v>
       </c>
@@ -7557,18 +7511,18 @@
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="227"/>
+      <c r="A20" s="187"/>
       <c r="B20" s="4" t="s">
         <v>227</v>
       </c>
       <c r="C20" s="113"/>
-      <c r="D20" s="247"/>
+      <c r="D20" s="202"/>
       <c r="E20" s="114"/>
-      <c r="F20" s="229" t="s">
+      <c r="F20" s="40" t="s">
         <v>114</v>
       </c>
       <c r="G20" s="34"/>
-      <c r="H20" s="228"/>
+      <c r="H20" s="188"/>
       <c r="M20" s="3" t="s">
         <v>271</v>
       </c>
@@ -7586,7 +7540,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="227">
+      <c r="A21" s="187">
         <f>'Sch 8 &amp; 9'!B34</f>
         <v>524117</v>
       </c>
@@ -7594,22 +7548,22 @@
         <v>145</v>
       </c>
       <c r="C21" s="34"/>
-      <c r="D21" s="247">
+      <c r="D21" s="202">
         <f>'Sch 8 &amp; 9'!D34</f>
-        <v>532719</v>
+        <v>726126</v>
       </c>
       <c r="E21" s="114">
         <f>37500+5000</f>
         <v>42500</v>
       </c>
-      <c r="F21" s="229" t="s">
+      <c r="F21" s="40" t="s">
         <v>266</v>
       </c>
       <c r="G21" s="34">
         <f>20000+5000</f>
         <v>25000</v>
       </c>
-      <c r="H21" s="228"/>
+      <c r="H21" s="188"/>
       <c r="M21" s="3" t="s">
         <v>273</v>
       </c>
@@ -7619,34 +7573,34 @@
       </c>
       <c r="O21" s="116">
         <f t="shared" ref="O21:P21" si="3">O13+O20</f>
-        <v>6148645</v>
+        <v>6342052</v>
       </c>
       <c r="P21" s="116">
         <f t="shared" si="3"/>
-        <v>687651.7</v>
+        <v>494244.7</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="227"/>
+      <c r="A22" s="187"/>
       <c r="B22" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="113"/>
-      <c r="D22" s="247"/>
+      <c r="D22" s="202"/>
       <c r="E22" s="117">
         <v>0</v>
       </c>
-      <c r="F22" s="229" t="s">
+      <c r="F22" s="40" t="s">
         <v>126</v>
       </c>
       <c r="G22" s="34">
         <f>10000</f>
         <v>10000</v>
       </c>
-      <c r="H22" s="228"/>
+      <c r="H22" s="188"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="227">
+      <c r="A23" s="187">
         <v>1342948</v>
       </c>
       <c r="B23" s="34" t="s">
@@ -7656,7 +7610,7 @@
         <f>1068130</f>
         <v>1068130</v>
       </c>
-      <c r="D23" s="247"/>
+      <c r="D23" s="202"/>
       <c r="E23" s="114">
         <v>896988</v>
       </c>
@@ -7666,13 +7620,13 @@
       <c r="G23" s="115">
         <v>896988</v>
       </c>
-      <c r="H23" s="228">
+      <c r="H23" s="188">
         <f>SUM(G21:G23)</f>
         <v>931988</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="227">
+      <c r="A24" s="187">
         <f>538285+64745</f>
         <v>603030</v>
       </c>
@@ -7683,14 +7637,14 @@
         <f>540480+15622+79302</f>
         <v>635404</v>
       </c>
-      <c r="D24" s="247"/>
+      <c r="D24" s="202"/>
       <c r="E24" s="114"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
-      <c r="H24" s="228"/>
+      <c r="H24" s="188"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="227">
+      <c r="A25" s="187">
         <f>'Sch 2'!K15</f>
         <v>70170.399999999994</v>
       </c>
@@ -7701,16 +7655,16 @@
         <f>+'Sch 2'!H15</f>
         <v>100773</v>
       </c>
-      <c r="D25" s="247"/>
+      <c r="D25" s="202"/>
       <c r="E25" s="114"/>
       <c r="F25" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G25" s="34"/>
-      <c r="H25" s="228"/>
+      <c r="H25" s="188"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="227">
+      <c r="A26" s="187">
         <v>77350</v>
       </c>
       <c r="B26" s="34" t="s">
@@ -7720,7 +7674,7 @@
         <f>Workings!D32</f>
         <v>67777</v>
       </c>
-      <c r="D26" s="247"/>
+      <c r="D26" s="202"/>
       <c r="E26" s="114">
         <v>2421</v>
       </c>
@@ -7728,13 +7682,13 @@
         <v>17</v>
       </c>
       <c r="G26" s="34"/>
-      <c r="H26" s="228">
+      <c r="H26" s="188">
         <f>2337</f>
         <v>2337</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="227">
+      <c r="A27" s="187">
         <v>7080</v>
       </c>
       <c r="B27" s="34" t="s">
@@ -7743,7 +7697,7 @@
       <c r="C27" s="113">
         <v>0</v>
       </c>
-      <c r="D27" s="247"/>
+      <c r="D27" s="202"/>
       <c r="E27" s="114">
         <f>257457</f>
         <v>257457</v>
@@ -7755,10 +7709,10 @@
         <f>308272+3149</f>
         <v>311421</v>
       </c>
-      <c r="H27" s="228"/>
+      <c r="H27" s="188"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="227">
+      <c r="A28" s="187">
         <v>6300</v>
       </c>
       <c r="B28" s="34" t="s">
@@ -7767,7 +7721,7 @@
       <c r="C28" s="113">
         <v>6300</v>
       </c>
-      <c r="D28" s="247"/>
+      <c r="D28" s="202"/>
       <c r="E28" s="114">
         <v>-66446</v>
       </c>
@@ -7777,10 +7731,10 @@
       <c r="G28" s="34">
         <v>74652</v>
       </c>
-      <c r="H28" s="228"/>
+      <c r="H28" s="188"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="227">
+      <c r="A29" s="187">
         <v>49235</v>
       </c>
       <c r="B29" s="34" t="s">
@@ -7790,7 +7744,7 @@
         <f>Workings!D38</f>
         <v>34775</v>
       </c>
-      <c r="D29" s="247">
+      <c r="D29" s="202">
         <f>SUM(C23:C29)</f>
         <v>1913159</v>
       </c>
@@ -7804,16 +7758,16 @@
         <f>105827+3149</f>
         <v>108976</v>
       </c>
-      <c r="H29" s="228"/>
+      <c r="H29" s="188"/>
       <c r="J29" s="24"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="227"/>
+      <c r="A30" s="187"/>
       <c r="B30" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="113"/>
-      <c r="D30" s="247"/>
+      <c r="D30" s="202"/>
       <c r="E30" s="114">
         <v>-99607</v>
       </c>
@@ -7823,10 +7777,10 @@
       <c r="G30" s="34">
         <v>104952</v>
       </c>
-      <c r="H30" s="228"/>
+      <c r="H30" s="188"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="227">
+      <c r="A31" s="187">
         <f>6596+51304-11000</f>
         <v>46900</v>
       </c>
@@ -7837,7 +7791,7 @@
         <f>6143+33248</f>
         <v>39391</v>
       </c>
-      <c r="D31" s="247"/>
+      <c r="D31" s="202"/>
       <c r="E31" s="114">
         <v>-1693</v>
       </c>
@@ -7847,10 +7801,10 @@
       <c r="G31" s="34">
         <v>2854</v>
       </c>
-      <c r="H31" s="228"/>
+      <c r="H31" s="188"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="227">
+      <c r="A32" s="187">
         <v>378184</v>
       </c>
       <c r="B32" s="34" t="s">
@@ -7860,7 +7814,7 @@
         <f>407766</f>
         <v>407766</v>
       </c>
-      <c r="D32" s="247"/>
+      <c r="D32" s="202"/>
       <c r="E32" s="114">
         <v>-16657</v>
       </c>
@@ -7870,10 +7824,10 @@
       <c r="G32" s="34">
         <v>17733</v>
       </c>
-      <c r="H32" s="228"/>
+      <c r="H32" s="188"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="227">
+      <c r="A33" s="187">
         <v>3750</v>
       </c>
       <c r="B33" s="34" t="s">
@@ -7883,7 +7837,7 @@
         <f>1260</f>
         <v>1260</v>
       </c>
-      <c r="D33" s="247"/>
+      <c r="D33" s="202"/>
       <c r="E33" s="114">
         <v>3693</v>
       </c>
@@ -7893,13 +7847,13 @@
       <c r="G33" s="115">
         <v>0</v>
       </c>
-      <c r="H33" s="228">
+      <c r="H33" s="188">
         <f>G27-SUM(G28:G32)+G33</f>
         <v>2254</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="227">
+      <c r="A34" s="187">
         <v>69000</v>
       </c>
       <c r="B34" s="34" t="s">
@@ -7909,14 +7863,14 @@
         <f>72456</f>
         <v>72456</v>
       </c>
-      <c r="D34" s="247"/>
+      <c r="D34" s="202"/>
       <c r="E34" s="114"/>
       <c r="F34" s="34"/>
       <c r="G34" s="34"/>
-      <c r="H34" s="228"/>
+      <c r="H34" s="188"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="227">
+      <c r="A35" s="187">
         <v>9502</v>
       </c>
       <c r="B35" s="34" t="s">
@@ -7926,16 +7880,16 @@
         <f>10032</f>
         <v>10032</v>
       </c>
-      <c r="D35" s="247"/>
+      <c r="D35" s="202"/>
       <c r="E35" s="114"/>
-      <c r="F35" s="229" t="s">
+      <c r="F35" s="40" t="s">
         <v>19</v>
       </c>
       <c r="G35" s="34"/>
-      <c r="H35" s="228"/>
+      <c r="H35" s="188"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="227">
+      <c r="A36" s="187">
         <v>80</v>
       </c>
       <c r="B36" s="34" t="s">
@@ -7944,21 +7898,21 @@
       <c r="C36" s="113">
         <v>0</v>
       </c>
-      <c r="D36" s="247"/>
+      <c r="D36" s="202"/>
       <c r="E36" s="114">
         <v>3000</v>
       </c>
-      <c r="F36" s="229" t="s">
+      <c r="F36" s="40" t="s">
         <v>20</v>
       </c>
       <c r="G36" s="34"/>
-      <c r="H36" s="228">
+      <c r="H36" s="188">
         <f>17500</f>
         <v>17500</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="227">
+      <c r="A37" s="187">
         <v>53000</v>
       </c>
       <c r="B37" s="34" t="s">
@@ -7968,21 +7922,21 @@
         <f>43000</f>
         <v>43000</v>
       </c>
-      <c r="D37" s="247"/>
+      <c r="D37" s="202"/>
       <c r="E37" s="117">
         <v>0</v>
       </c>
-      <c r="F37" s="229" t="s">
+      <c r="F37" s="40" t="s">
         <v>406</v>
       </c>
       <c r="G37" s="34"/>
-      <c r="H37" s="228">
+      <c r="H37" s="188">
         <f>52238-12500</f>
         <v>39738</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="227">
+      <c r="A38" s="187">
         <v>1350</v>
       </c>
       <c r="B38" s="34" t="s">
@@ -7992,14 +7946,14 @@
         <f>6800</f>
         <v>6800</v>
       </c>
-      <c r="D38" s="247"/>
+      <c r="D38" s="202"/>
       <c r="E38" s="114"/>
-      <c r="F38" s="229"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="34"/>
-      <c r="H38" s="228"/>
+      <c r="H38" s="188"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="227">
+      <c r="A39" s="187">
         <v>1298</v>
       </c>
       <c r="B39" s="34" t="s">
@@ -8009,14 +7963,14 @@
         <f>59</f>
         <v>59</v>
       </c>
-      <c r="D39" s="247"/>
+      <c r="D39" s="202"/>
       <c r="E39" s="114"/>
-      <c r="F39" s="229"/>
+      <c r="F39" s="40"/>
       <c r="G39" s="34"/>
-      <c r="H39" s="228"/>
+      <c r="H39" s="188"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="227">
+      <c r="A40" s="187">
         <v>1000</v>
       </c>
       <c r="B40" s="34" t="s">
@@ -8026,14 +7980,14 @@
         <f>3961</f>
         <v>3961</v>
       </c>
-      <c r="D40" s="247"/>
+      <c r="D40" s="202"/>
       <c r="E40" s="114"/>
-      <c r="F40" s="229"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="34"/>
-      <c r="H40" s="228"/>
+      <c r="H40" s="188"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="227">
+      <c r="A41" s="187">
         <v>95788</v>
       </c>
       <c r="B41" s="34" t="s">
@@ -8043,14 +7997,14 @@
         <f>Workings!D83+617</f>
         <v>113247</v>
       </c>
-      <c r="D41" s="247"/>
+      <c r="D41" s="202"/>
       <c r="E41" s="114"/>
-      <c r="F41" s="229"/>
+      <c r="F41" s="40"/>
       <c r="G41" s="34"/>
-      <c r="H41" s="228"/>
+      <c r="H41" s="188"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="227">
+      <c r="A42" s="187">
         <v>391309</v>
       </c>
       <c r="B42" s="34" t="s">
@@ -8060,14 +8014,14 @@
         <f>400607</f>
         <v>400607</v>
       </c>
-      <c r="D42" s="247"/>
+      <c r="D42" s="202"/>
       <c r="E42" s="114"/>
-      <c r="F42" s="229"/>
+      <c r="F42" s="40"/>
       <c r="G42" s="34"/>
-      <c r="H42" s="228"/>
+      <c r="H42" s="188"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="227">
+      <c r="A43" s="187">
         <f>307687-29500+11000+25000-53000</f>
         <v>261187</v>
       </c>
@@ -8078,45 +8032,45 @@
         <f>330009</f>
         <v>330009</v>
       </c>
-      <c r="D43" s="247">
+      <c r="D43" s="202">
         <f>SUM(C31:C43)</f>
         <v>1428588</v>
       </c>
       <c r="E43" s="114"/>
-      <c r="F43" s="229"/>
+      <c r="F43" s="40"/>
       <c r="G43" s="34"/>
-      <c r="H43" s="228"/>
+      <c r="H43" s="188"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="227"/>
+      <c r="A44" s="187"/>
       <c r="B44" s="34"/>
       <c r="C44" s="113"/>
-      <c r="D44" s="247"/>
+      <c r="D44" s="202"/>
       <c r="E44" s="114"/>
-      <c r="F44" s="229"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="34"/>
-      <c r="H44" s="228"/>
+      <c r="H44" s="188"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="227">
+      <c r="A45" s="187">
         <f>ROUND((E47-SUM(A7:A44))*25%,0)</f>
         <v>171150</v>
       </c>
-      <c r="B45" s="230" t="s">
+      <c r="B45" s="189" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="113"/>
-      <c r="D45" s="247">
+      <c r="D45" s="202">
         <f>ROUND((H47-SUM(D7:D44))*25%,0)</f>
-        <v>182865</v>
+        <v>134513</v>
       </c>
       <c r="E45" s="114"/>
-      <c r="F45" s="229"/>
+      <c r="F45" s="40"/>
       <c r="G45" s="34"/>
-      <c r="H45" s="228"/>
+      <c r="H45" s="188"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="227">
+      <c r="A46" s="187">
         <f>E47-SUM(A7:A45)</f>
         <v>513449.59999999963</v>
       </c>
@@ -8124,48 +8078,46 @@
         <v>8</v>
       </c>
       <c r="C46" s="120"/>
-      <c r="D46" s="247">
+      <c r="D46" s="202">
         <f>H47-SUM(D7:D45)</f>
-        <v>548593</v>
+        <v>403538</v>
       </c>
       <c r="E46" s="114"/>
-      <c r="F46" s="229"/>
+      <c r="F46" s="40"/>
       <c r="G46" s="34"/>
-      <c r="H46" s="228"/>
+      <c r="H46" s="188"/>
     </row>
     <row r="47" spans="1:8" s="32" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="219">
+      <c r="A47" s="183">
         <f>SUM(A7:A46)</f>
         <v>6813728</v>
       </c>
-      <c r="B47" s="218" t="s">
+      <c r="B47" s="288" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="218"/>
-      <c r="D47" s="248">
+      <c r="C47" s="288"/>
+      <c r="D47" s="203">
         <f>SUM(D7:D46)</f>
         <v>6880103</v>
       </c>
-      <c r="E47" s="245">
+      <c r="E47" s="200">
         <f>SUM(E7:E46)</f>
         <v>6813728</v>
       </c>
-      <c r="F47" s="218" t="s">
+      <c r="F47" s="288" t="s">
         <v>9</v>
       </c>
-      <c r="G47" s="218"/>
-      <c r="H47" s="220">
+      <c r="G47" s="288"/>
+      <c r="H47" s="184">
         <f>SUM(H7:H46)</f>
         <v>6880103</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="231"/>
-      <c r="B48" s="232"/>
+      <c r="A48" s="161"/>
       <c r="C48" s="23"/>
       <c r="D48" s="23"/>
       <c r="E48" s="23"/>
-      <c r="F48" s="232"/>
       <c r="G48" s="23">
         <f>A47-E47</f>
         <v>0</v>
@@ -8176,117 +8128,117 @@
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="178" t="s">
+      <c r="A49" s="162" t="s">
         <v>495</v>
       </c>
-      <c r="B49" s="179"/>
-      <c r="C49" s="180"/>
-      <c r="D49" s="179"/>
-      <c r="E49" s="233" t="s">
+      <c r="B49" s="163"/>
+      <c r="C49" s="164"/>
+      <c r="D49" s="163"/>
+      <c r="E49" s="296" t="s">
         <v>496</v>
       </c>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="234"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="297"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="178"/>
-      <c r="B50" s="179"/>
-      <c r="C50" s="180"/>
-      <c r="D50" s="179"/>
-      <c r="E50" s="179"/>
-      <c r="F50" s="179"/>
-      <c r="G50" s="179"/>
-      <c r="H50" s="185"/>
+      <c r="A50" s="162"/>
+      <c r="B50" s="163"/>
+      <c r="C50" s="164"/>
+      <c r="D50" s="163"/>
+      <c r="E50" s="163"/>
+      <c r="F50" s="163"/>
+      <c r="G50" s="163"/>
+      <c r="H50" s="168"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="178"/>
-      <c r="B51" s="179"/>
-      <c r="C51" s="180"/>
-      <c r="D51" s="179"/>
-      <c r="E51" s="179"/>
-      <c r="F51" s="186"/>
-      <c r="G51" s="186"/>
-      <c r="H51" s="187"/>
+      <c r="A51" s="162"/>
+      <c r="B51" s="163"/>
+      <c r="C51" s="164"/>
+      <c r="D51" s="163"/>
+      <c r="E51" s="163"/>
+      <c r="F51" s="169"/>
+      <c r="G51" s="169"/>
+      <c r="H51" s="170"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A52" s="178"/>
-      <c r="B52" s="179"/>
-      <c r="C52" s="180"/>
-      <c r="D52" s="179"/>
-      <c r="E52" s="179"/>
-      <c r="F52" s="186"/>
-      <c r="G52" s="186"/>
-      <c r="H52" s="187"/>
+      <c r="A52" s="162"/>
+      <c r="B52" s="163"/>
+      <c r="C52" s="164"/>
+      <c r="D52" s="163"/>
+      <c r="E52" s="163"/>
+      <c r="F52" s="169"/>
+      <c r="G52" s="169"/>
+      <c r="H52" s="170"/>
     </row>
     <row r="53" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="191" t="s">
+      <c r="A53" s="174" t="s">
         <v>497</v>
       </c>
-      <c r="B53" s="189"/>
-      <c r="C53" s="190"/>
-      <c r="D53" s="179"/>
-      <c r="E53" s="179"/>
-      <c r="F53" s="186"/>
-      <c r="G53" s="186"/>
-      <c r="H53" s="187"/>
+      <c r="B53" s="172"/>
+      <c r="C53" s="173"/>
+      <c r="D53" s="163"/>
+      <c r="E53" s="163"/>
+      <c r="F53" s="169"/>
+      <c r="G53" s="169"/>
+      <c r="H53" s="170"/>
     </row>
     <row r="54" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="191" t="s">
+      <c r="A54" s="174" t="s">
         <v>498</v>
       </c>
-      <c r="B54" s="189"/>
-      <c r="C54" s="190"/>
-      <c r="D54" s="179"/>
-      <c r="E54" s="233" t="s">
+      <c r="B54" s="172"/>
+      <c r="C54" s="173"/>
+      <c r="D54" s="163"/>
+      <c r="E54" s="296" t="s">
         <v>499</v>
       </c>
-      <c r="F54" s="233"/>
-      <c r="G54" s="233"/>
-      <c r="H54" s="234"/>
+      <c r="F54" s="296"/>
+      <c r="G54" s="296"/>
+      <c r="H54" s="297"/>
     </row>
     <row r="55" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="191" t="s">
+      <c r="A55" s="174" t="s">
         <v>500</v>
       </c>
-      <c r="B55" s="189"/>
-      <c r="C55" s="190"/>
-      <c r="D55" s="179"/>
-      <c r="E55" s="186"/>
-      <c r="F55" s="186"/>
-      <c r="G55" s="186"/>
-      <c r="H55" s="187"/>
+      <c r="B55" s="172"/>
+      <c r="C55" s="173"/>
+      <c r="D55" s="163"/>
+      <c r="E55" s="169"/>
+      <c r="F55" s="169"/>
+      <c r="G55" s="169"/>
+      <c r="H55" s="170"/>
       <c r="J55" s="135"/>
     </row>
-    <row r="56" spans="1:13" s="183" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A56" s="192">
-        <v>46221</v>
-      </c>
-      <c r="B56" s="193"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="179"/>
-      <c r="E56" s="179"/>
-      <c r="F56" s="179"/>
-      <c r="G56" s="179"/>
-      <c r="H56" s="185"/>
-      <c r="I56" s="180"/>
-      <c r="J56" s="179"/>
-      <c r="K56" s="179"/>
-      <c r="L56" s="182"/>
-      <c r="M56" s="182"/>
-    </row>
-    <row r="57" spans="1:13" s="179" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="194"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="195"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="195"/>
-      <c r="G57" s="195"/>
-      <c r="H57" s="197"/>
-      <c r="I57" s="180"/>
-    </row>
-    <row r="58" spans="1:13" s="179" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" s="166" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A56" s="282">
+        <v>46229</v>
+      </c>
+      <c r="B56" s="283"/>
+      <c r="C56" s="283"/>
+      <c r="D56" s="163"/>
+      <c r="E56" s="163"/>
+      <c r="F56" s="163"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="168"/>
+      <c r="I56" s="164"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="163"/>
+      <c r="L56" s="165"/>
+      <c r="M56" s="165"/>
+    </row>
+    <row r="57" spans="1:13" s="163" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="175"/>
+      <c r="B57" s="176"/>
+      <c r="C57" s="177"/>
+      <c r="D57" s="176"/>
+      <c r="E57" s="177"/>
+      <c r="F57" s="176"/>
+      <c r="G57" s="176"/>
+      <c r="H57" s="178"/>
+      <c r="I57" s="164"/>
+    </row>
+    <row r="58" spans="1:13" s="163" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="37"/>
       <c r="B58"/>
       <c r="C58" s="122"/>
@@ -8295,9 +8247,9 @@
       <c r="F58"/>
       <c r="G58" s="122"/>
       <c r="H58" s="118"/>
-      <c r="I58" s="180"/>
-    </row>
-    <row r="59" spans="1:13" s="179" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="164"/>
+    </row>
+    <row r="59" spans="1:13" s="163" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="37"/>
       <c r="B59"/>
       <c r="C59" s="122"/>
@@ -8306,9 +8258,9 @@
       <c r="F59"/>
       <c r="G59" s="122"/>
       <c r="H59" s="118"/>
-      <c r="I59" s="180"/>
-    </row>
-    <row r="60" spans="1:13" s="179" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="164"/>
+    </row>
+    <row r="60" spans="1:13" s="163" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="37"/>
       <c r="B60"/>
       <c r="C60" s="122"/>
@@ -8317,9 +8269,9 @@
       <c r="F60"/>
       <c r="G60" s="122"/>
       <c r="H60" s="118"/>
-      <c r="I60" s="180"/>
-    </row>
-    <row r="61" spans="1:13" s="179" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="164"/>
+    </row>
+    <row r="61" spans="1:13" s="163" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="37"/>
       <c r="B61"/>
       <c r="C61" s="122"/>
@@ -8328,9 +8280,9 @@
       <c r="F61"/>
       <c r="G61" s="122"/>
       <c r="H61" s="118"/>
-      <c r="I61" s="180"/>
-    </row>
-    <row r="62" spans="1:13" s="179" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="164"/>
+    </row>
+    <row r="62" spans="1:13" s="163" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="37"/>
       <c r="B62"/>
       <c r="C62" s="122"/>
@@ -8339,9 +8291,9 @@
       <c r="F62"/>
       <c r="G62" s="122"/>
       <c r="H62" s="118"/>
-      <c r="I62" s="180"/>
-    </row>
-    <row r="63" spans="1:13" s="179" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I62" s="164"/>
+    </row>
+    <row r="63" spans="1:13" s="163" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="37"/>
       <c r="B63"/>
       <c r="C63" s="122"/>
@@ -8350,9 +8302,9 @@
       <c r="F63"/>
       <c r="G63" s="122"/>
       <c r="H63" s="118"/>
-      <c r="I63" s="180"/>
-    </row>
-    <row r="64" spans="1:13" s="179" customFormat="1" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I63" s="164"/>
+    </row>
+    <row r="64" spans="1:13" s="163" customFormat="1" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="37"/>
       <c r="B64"/>
       <c r="C64" s="122"/>
@@ -8361,7 +8313,7 @@
       <c r="F64"/>
       <c r="G64" s="122"/>
       <c r="H64" s="118"/>
-      <c r="I64" s="180"/>
+      <c r="I64" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -8400,43 +8352,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="249" t="str">
+      <c r="A1" s="301" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="249"/>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
-      <c r="F1" s="249"/>
-      <c r="G1" s="249"/>
-      <c r="H1" s="249"/>
-      <c r="I1" s="249"/>
-      <c r="J1" s="249"/>
-      <c r="K1" s="249"/>
-      <c r="L1" s="249"/>
-      <c r="M1" s="249"/>
-      <c r="N1" s="249"/>
-      <c r="O1" s="249"/>
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="301"/>
+      <c r="L1" s="301"/>
+      <c r="M1" s="301"/>
+      <c r="N1" s="301"/>
+      <c r="O1" s="301"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="302" t="s">
         <v>388</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="166"/>
+      <c r="B2" s="302"/>
+      <c r="C2" s="302"/>
+      <c r="D2" s="302"/>
+      <c r="E2" s="302"/>
+      <c r="F2" s="302"/>
+      <c r="G2" s="302"/>
+      <c r="H2" s="302"/>
+      <c r="I2" s="302"/>
+      <c r="J2" s="302"/>
+      <c r="K2" s="302"/>
+      <c r="L2" s="302"/>
+      <c r="M2" s="302"/>
+      <c r="N2" s="302"/>
+      <c r="O2" s="302"/>
     </row>
     <row r="3" spans="1:15" s="71" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="69" t="s">
@@ -8897,47 +8849,47 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="258" t="s">
+      <c r="A13" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B13" s="259"/>
-      <c r="C13" s="259"/>
-      <c r="D13" s="259"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="251">
+      <c r="B13" s="306"/>
+      <c r="C13" s="306"/>
+      <c r="D13" s="306"/>
+      <c r="E13" s="307"/>
+      <c r="F13" s="205">
         <f>SUM(F5:F12)</f>
         <v>1705887</v>
       </c>
-      <c r="G13" s="251">
+      <c r="G13" s="205">
         <f t="shared" ref="G13:O13" si="6">SUM(G5:G12)</f>
         <v>109</v>
       </c>
-      <c r="H13" s="251">
+      <c r="H13" s="205">
         <f t="shared" si="6"/>
         <v>21460</v>
       </c>
-      <c r="I13" s="251">
+      <c r="I13" s="205">
         <f t="shared" si="6"/>
         <v>39431</v>
       </c>
-      <c r="J13" s="251">
+      <c r="J13" s="205">
         <f t="shared" si="6"/>
         <v>46230</v>
       </c>
-      <c r="K13" s="251">
+      <c r="K13" s="205">
         <f t="shared" si="6"/>
         <v>77637</v>
       </c>
-      <c r="L13" s="251">
+      <c r="L13" s="205">
         <f t="shared" si="6"/>
         <v>184867</v>
       </c>
-      <c r="M13" s="251">
+      <c r="M13" s="205">
         <f t="shared" si="6"/>
         <v>1890754</v>
       </c>
-      <c r="N13" s="250"/>
-      <c r="O13" s="251">
+      <c r="N13" s="204"/>
+      <c r="O13" s="205">
         <f t="shared" si="6"/>
         <v>2244578</v>
       </c>
@@ -9101,47 +9053,47 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="258" t="s">
+      <c r="A19" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B19" s="259"/>
-      <c r="C19" s="259"/>
-      <c r="D19" s="259"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="251">
+      <c r="B19" s="306"/>
+      <c r="C19" s="306"/>
+      <c r="D19" s="306"/>
+      <c r="E19" s="307"/>
+      <c r="F19" s="205">
         <f>SUM(F16:F18)</f>
         <v>1556075</v>
       </c>
-      <c r="G19" s="251">
+      <c r="G19" s="205">
         <f t="shared" ref="G19:M19" si="9">SUM(G16:G18)</f>
         <v>327</v>
       </c>
-      <c r="H19" s="251">
+      <c r="H19" s="205">
         <f t="shared" si="9"/>
         <v>65944</v>
       </c>
-      <c r="I19" s="251">
+      <c r="I19" s="205">
         <f t="shared" si="9"/>
         <v>75834</v>
       </c>
-      <c r="J19" s="251">
+      <c r="J19" s="205">
         <f t="shared" si="9"/>
         <v>78084</v>
       </c>
-      <c r="K19" s="251">
+      <c r="K19" s="205">
         <f t="shared" ref="K19:L19" si="10">SUM(K13:K18)</f>
         <v>159936</v>
       </c>
-      <c r="L19" s="251">
+      <c r="L19" s="205">
         <f t="shared" si="10"/>
         <v>487355</v>
       </c>
-      <c r="M19" s="251">
+      <c r="M19" s="205">
         <f t="shared" si="9"/>
         <v>1858563</v>
       </c>
-      <c r="N19" s="252"/>
-      <c r="O19" s="251">
+      <c r="N19" s="206"/>
+      <c r="O19" s="205">
         <f>SUM(O16:O18)</f>
         <v>2020540</v>
       </c>
@@ -9475,47 +9427,47 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="258" t="s">
+      <c r="A28" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B28" s="259"/>
-      <c r="C28" s="259"/>
-      <c r="D28" s="259"/>
-      <c r="E28" s="260"/>
-      <c r="F28" s="251">
+      <c r="B28" s="306"/>
+      <c r="C28" s="306"/>
+      <c r="D28" s="306"/>
+      <c r="E28" s="307"/>
+      <c r="F28" s="205">
         <f>SUM(F22:F27)</f>
         <v>1065174</v>
       </c>
-      <c r="G28" s="251">
+      <c r="G28" s="205">
         <f t="shared" ref="G28:O28" si="13">SUM(G22:G27)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="251">
+      <c r="H28" s="205">
         <f t="shared" si="13"/>
         <v>10025</v>
       </c>
-      <c r="I28" s="251">
+      <c r="I28" s="205">
         <f t="shared" si="13"/>
         <v>22906</v>
       </c>
-      <c r="J28" s="251">
+      <c r="J28" s="205">
         <f t="shared" si="13"/>
         <v>24221</v>
       </c>
-      <c r="K28" s="251">
+      <c r="K28" s="205">
         <f t="shared" si="13"/>
         <v>31244</v>
       </c>
-      <c r="L28" s="251">
+      <c r="L28" s="205">
         <f t="shared" si="13"/>
         <v>88396</v>
       </c>
-      <c r="M28" s="251">
+      <c r="M28" s="205">
         <f t="shared" si="13"/>
         <v>1153570</v>
       </c>
-      <c r="N28" s="252"/>
-      <c r="O28" s="251">
+      <c r="N28" s="206"/>
+      <c r="O28" s="205">
         <f t="shared" si="13"/>
         <v>1279702</v>
       </c>
@@ -9597,47 +9549,47 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="258" t="s">
+      <c r="A32" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B32" s="259"/>
-      <c r="C32" s="259"/>
-      <c r="D32" s="259"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="251">
+      <c r="B32" s="306"/>
+      <c r="C32" s="306"/>
+      <c r="D32" s="306"/>
+      <c r="E32" s="307"/>
+      <c r="F32" s="205">
         <f>SUM(F31)</f>
         <v>31500</v>
       </c>
-      <c r="G32" s="251">
+      <c r="G32" s="205">
         <f t="shared" ref="G32:M32" si="16">SUM(G31)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="251">
+      <c r="H32" s="205">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I32" s="251">
+      <c r="I32" s="205">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J32" s="251">
+      <c r="J32" s="205">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K32" s="251">
+      <c r="K32" s="205">
         <f t="shared" ref="K32:L32" si="17">SUM(K26:K31)</f>
         <v>32403</v>
       </c>
-      <c r="L32" s="251">
+      <c r="L32" s="205">
         <f t="shared" si="17"/>
         <v>89555</v>
       </c>
-      <c r="M32" s="251">
+      <c r="M32" s="205">
         <f t="shared" si="16"/>
         <v>31524</v>
       </c>
-      <c r="N32" s="252"/>
-      <c r="O32" s="251">
+      <c r="N32" s="206"/>
+      <c r="O32" s="205">
         <f>SUM(O31)</f>
         <v>31500</v>
       </c>
@@ -9720,47 +9672,47 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="258" t="s">
+      <c r="A36" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B36" s="259"/>
-      <c r="C36" s="259"/>
-      <c r="D36" s="259"/>
-      <c r="E36" s="260"/>
-      <c r="F36" s="251">
+      <c r="B36" s="306"/>
+      <c r="C36" s="306"/>
+      <c r="D36" s="306"/>
+      <c r="E36" s="307"/>
+      <c r="F36" s="205">
         <f>SUM(F35:F35)</f>
         <v>15124</v>
       </c>
-      <c r="G36" s="251">
+      <c r="G36" s="205">
         <f t="shared" ref="G36:O36" si="20">SUM(G35:G35)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="251">
+      <c r="H36" s="205">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="I36" s="251">
+      <c r="I36" s="205">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J36" s="251">
+      <c r="J36" s="205">
         <f t="shared" si="20"/>
         <v>12</v>
       </c>
-      <c r="K36" s="251">
+      <c r="K36" s="205">
         <f t="shared" si="20"/>
         <v>979</v>
       </c>
-      <c r="L36" s="251">
+      <c r="L36" s="205">
         <f t="shared" si="20"/>
         <v>991</v>
       </c>
-      <c r="M36" s="251">
+      <c r="M36" s="205">
         <f t="shared" si="20"/>
         <v>16115</v>
       </c>
-      <c r="N36" s="252"/>
-      <c r="O36" s="251">
+      <c r="N36" s="206"/>
+      <c r="O36" s="205">
         <f t="shared" si="20"/>
         <v>21362</v>
       </c>
@@ -9842,47 +9794,47 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="258" t="s">
+      <c r="A40" s="305" t="s">
         <v>501</v>
       </c>
-      <c r="B40" s="259"/>
-      <c r="C40" s="259"/>
-      <c r="D40" s="259"/>
-      <c r="E40" s="260"/>
-      <c r="F40" s="251">
+      <c r="B40" s="306"/>
+      <c r="C40" s="306"/>
+      <c r="D40" s="306"/>
+      <c r="E40" s="307"/>
+      <c r="F40" s="205">
         <f>SUM(F39)</f>
         <v>255952</v>
       </c>
-      <c r="G40" s="251">
+      <c r="G40" s="205">
         <f t="shared" ref="G40:M40" si="23">SUM(G39)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="251">
+      <c r="H40" s="205">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="I40" s="251">
+      <c r="I40" s="205">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="J40" s="251">
+      <c r="J40" s="205">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K40" s="251">
+      <c r="K40" s="205">
         <f>SUM(K35:K39)</f>
         <v>2154</v>
       </c>
-      <c r="L40" s="251">
+      <c r="L40" s="205">
         <f>SUM(L35:L39)</f>
         <v>2178</v>
       </c>
-      <c r="M40" s="251">
+      <c r="M40" s="205">
         <f t="shared" si="23"/>
         <v>256148</v>
       </c>
-      <c r="N40" s="252"/>
-      <c r="O40" s="251">
+      <c r="N40" s="206"/>
+      <c r="O40" s="205">
         <f>SUM(O39)</f>
         <v>290034</v>
       </c>
@@ -9899,47 +9851,47 @@
       <c r="O41" s="62"/>
     </row>
     <row r="42" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="253" t="s">
+      <c r="A42" s="303" t="s">
         <v>502</v>
       </c>
-      <c r="B42" s="254"/>
-      <c r="C42" s="254"/>
-      <c r="D42" s="254"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="255">
+      <c r="B42" s="304"/>
+      <c r="C42" s="304"/>
+      <c r="D42" s="304"/>
+      <c r="E42" s="304"/>
+      <c r="F42" s="208">
         <f t="shared" ref="F42:M42" si="24">F13+F19+F28+F32+F36+F40</f>
         <v>4629712</v>
       </c>
-      <c r="G42" s="255">
+      <c r="G42" s="208">
         <f t="shared" si="24"/>
         <v>436</v>
       </c>
-      <c r="H42" s="255">
+      <c r="H42" s="208">
         <f t="shared" si="24"/>
         <v>97429</v>
       </c>
-      <c r="I42" s="255">
+      <c r="I42" s="208">
         <f t="shared" si="24"/>
         <v>138171</v>
       </c>
-      <c r="J42" s="255">
+      <c r="J42" s="208">
         <f t="shared" si="24"/>
         <v>148547</v>
       </c>
-      <c r="K42" s="255">
+      <c r="K42" s="208">
         <f t="shared" si="24"/>
         <v>304353</v>
       </c>
-      <c r="L42" s="255">
+      <c r="L42" s="208">
         <f t="shared" si="24"/>
         <v>853342</v>
       </c>
-      <c r="M42" s="255">
+      <c r="M42" s="208">
         <f t="shared" si="24"/>
         <v>5206674</v>
       </c>
-      <c r="N42" s="256"/>
-      <c r="O42" s="257">
+      <c r="N42" s="209"/>
+      <c r="O42" s="210">
         <f>O13+O19+O28+O32+O36+O40</f>
         <v>5887716</v>
       </c>
@@ -9969,130 +9921,130 @@
   <cols>
     <col min="1" max="1" width="5.21875" style="12" customWidth="1"/>
     <col min="2" max="2" width="28.109375" style="108" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="12.77734375" style="272" customWidth="1"/>
+    <col min="3" max="9" width="12.77734375" style="217" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" style="108"/>
     <col min="11" max="11" width="10" style="108" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="108"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="263" t="str">
+      <c r="A1" s="314" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
-      <c r="I1" s="263"/>
+      <c r="B1" s="314"/>
+      <c r="C1" s="314"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
+      <c r="G1" s="314"/>
+      <c r="H1" s="314"/>
+      <c r="I1" s="314"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="263"/>
-      <c r="B2" s="263"/>
-      <c r="C2" s="263"/>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="263"/>
-      <c r="I2" s="263"/>
+      <c r="A2" s="314"/>
+      <c r="B2" s="314"/>
+      <c r="C2" s="314"/>
+      <c r="D2" s="314"/>
+      <c r="E2" s="314"/>
+      <c r="F2" s="314"/>
+      <c r="G2" s="314"/>
+      <c r="H2" s="314"/>
+      <c r="I2" s="314"/>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="261" t="s">
+      <c r="A3" s="308" t="s">
         <v>382</v>
       </c>
-      <c r="B3" s="261"/>
-      <c r="C3" s="261"/>
-      <c r="D3" s="261"/>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="261"/>
-      <c r="I3" s="261"/>
+      <c r="B3" s="308"/>
+      <c r="C3" s="308"/>
+      <c r="D3" s="308"/>
+      <c r="E3" s="308"/>
+      <c r="F3" s="308"/>
+      <c r="G3" s="308"/>
+      <c r="H3" s="308"/>
+      <c r="I3" s="308"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="169" t="s">
+      <c r="A4" s="312" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="169" t="s">
+      <c r="B4" s="312" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="167" t="s">
+      <c r="C4" s="309" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167" t="s">
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="167"/>
-      <c r="I4" s="168" t="s">
+      <c r="H4" s="309"/>
+      <c r="I4" s="310" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="20" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="265"/>
-      <c r="B5" s="265"/>
-      <c r="C5" s="266" t="s">
+      <c r="A5" s="313"/>
+      <c r="B5" s="313"/>
+      <c r="C5" s="212" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="266" t="s">
+      <c r="D5" s="212" t="s">
         <v>379</v>
       </c>
-      <c r="E5" s="266" t="s">
+      <c r="E5" s="212" t="s">
         <v>380</v>
       </c>
-      <c r="F5" s="266" t="s">
+      <c r="F5" s="212" t="s">
         <v>381</v>
       </c>
-      <c r="G5" s="266" t="s">
+      <c r="G5" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="266" t="s">
+      <c r="H5" s="212" t="s">
         <v>375</v>
       </c>
-      <c r="I5" s="267"/>
+      <c r="I5" s="311"/>
       <c r="K5" s="106" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="268">
+      <c r="A6" s="213">
         <v>1</v>
       </c>
-      <c r="B6" s="269" t="s">
+      <c r="B6" s="214" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="270">
+      <c r="C6" s="215">
         <v>17729</v>
       </c>
-      <c r="D6" s="270">
-        <v>0</v>
-      </c>
-      <c r="E6" s="270">
+      <c r="D6" s="215">
+        <v>0</v>
+      </c>
+      <c r="E6" s="215">
         <f>11653</f>
         <v>11653</v>
       </c>
-      <c r="F6" s="270">
+      <c r="F6" s="215">
         <f>C6+D6+E6</f>
         <v>29382</v>
       </c>
-      <c r="G6" s="271">
+      <c r="G6" s="216">
         <v>0.4</v>
       </c>
-      <c r="H6" s="270">
+      <c r="H6" s="215">
         <f>ROUND(SUM(C6:D6,E6/2)*G6,)</f>
         <v>9422</v>
       </c>
-      <c r="I6" s="270">
+      <c r="I6" s="215">
         <f>F6-H6</f>
         <v>19960</v>
       </c>
-      <c r="K6" s="272">
+      <c r="K6" s="217">
         <v>11820</v>
       </c>
     </row>
@@ -10100,35 +10052,35 @@
       <c r="A7" s="21">
         <v>2</v>
       </c>
-      <c r="B7" s="273" t="s">
+      <c r="B7" s="218" t="s">
         <v>471</v>
       </c>
-      <c r="C7" s="274">
+      <c r="C7" s="219">
         <v>2224</v>
       </c>
-      <c r="D7" s="274">
-        <v>0</v>
-      </c>
-      <c r="E7" s="274">
+      <c r="D7" s="219">
+        <v>0</v>
+      </c>
+      <c r="E7" s="219">
         <f>53389</f>
         <v>53389</v>
       </c>
-      <c r="F7" s="274">
+      <c r="F7" s="219">
         <f t="shared" ref="F7:F13" si="0">C7+D7+E7</f>
         <v>55613</v>
       </c>
-      <c r="G7" s="275">
+      <c r="G7" s="220">
         <v>0.15</v>
       </c>
-      <c r="H7" s="274">
+      <c r="H7" s="219">
         <f t="shared" ref="H7:H12" si="1">ROUND(SUM(C7:D7,E7/2)*G7,)</f>
         <v>4338</v>
       </c>
-      <c r="I7" s="274">
+      <c r="I7" s="219">
         <f t="shared" ref="I7:I13" si="2">F7-H7</f>
         <v>51275</v>
       </c>
-      <c r="K7" s="272">
+      <c r="K7" s="217">
         <v>393</v>
       </c>
     </row>
@@ -10136,35 +10088,35 @@
       <c r="A8" s="21">
         <v>3</v>
       </c>
-      <c r="B8" s="273" t="s">
+      <c r="B8" s="218" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="274">
+      <c r="C8" s="219">
         <v>79317</v>
       </c>
-      <c r="D8" s="274">
-        <v>0</v>
-      </c>
-      <c r="E8" s="274">
+      <c r="D8" s="219">
+        <v>0</v>
+      </c>
+      <c r="E8" s="219">
         <f>5160+7250+66550</f>
         <v>78960</v>
       </c>
-      <c r="F8" s="274">
+      <c r="F8" s="219">
         <f t="shared" si="0"/>
         <v>158277</v>
       </c>
-      <c r="G8" s="275">
+      <c r="G8" s="220">
         <v>0.15</v>
       </c>
-      <c r="H8" s="274">
+      <c r="H8" s="219">
         <f t="shared" si="1"/>
         <v>17820</v>
       </c>
-      <c r="I8" s="274">
+      <c r="I8" s="219">
         <f t="shared" si="2"/>
         <v>140457</v>
       </c>
-      <c r="K8" s="272">
+      <c r="K8" s="217">
         <v>9608</v>
       </c>
     </row>
@@ -10172,34 +10124,34 @@
       <c r="A9" s="21">
         <v>4</v>
       </c>
-      <c r="B9" s="273" t="s">
+      <c r="B9" s="218" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="274">
+      <c r="C9" s="219">
         <v>8956</v>
       </c>
-      <c r="D9" s="274">
-        <v>0</v>
-      </c>
-      <c r="E9" s="274">
-        <v>0</v>
-      </c>
-      <c r="F9" s="274">
+      <c r="D9" s="219">
+        <v>0</v>
+      </c>
+      <c r="E9" s="219">
+        <v>0</v>
+      </c>
+      <c r="F9" s="219">
         <f t="shared" si="0"/>
         <v>8956</v>
       </c>
-      <c r="G9" s="275">
+      <c r="G9" s="220">
         <v>0.15</v>
       </c>
-      <c r="H9" s="274">
+      <c r="H9" s="219">
         <f t="shared" si="1"/>
         <v>1343</v>
       </c>
-      <c r="I9" s="274">
+      <c r="I9" s="219">
         <f t="shared" si="2"/>
         <v>7613</v>
       </c>
-      <c r="K9" s="272">
+      <c r="K9" s="217">
         <v>1580</v>
       </c>
     </row>
@@ -10207,35 +10159,35 @@
       <c r="A10" s="21">
         <v>5</v>
       </c>
-      <c r="B10" s="273" t="s">
+      <c r="B10" s="218" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="274">
+      <c r="C10" s="219">
         <v>35586</v>
       </c>
-      <c r="D10" s="274">
+      <c r="D10" s="219">
         <f>8950</f>
         <v>8950</v>
       </c>
-      <c r="E10" s="274">
-        <v>0</v>
-      </c>
-      <c r="F10" s="274">
+      <c r="E10" s="219">
+        <v>0</v>
+      </c>
+      <c r="F10" s="219">
         <f t="shared" si="0"/>
         <v>44536</v>
       </c>
-      <c r="G10" s="275">
+      <c r="G10" s="220">
         <v>0.15</v>
       </c>
-      <c r="H10" s="274">
+      <c r="H10" s="219">
         <f t="shared" si="1"/>
         <v>6680</v>
       </c>
-      <c r="I10" s="274">
+      <c r="I10" s="219">
         <f t="shared" si="2"/>
         <v>37856</v>
       </c>
-      <c r="K10" s="272">
+      <c r="K10" s="217">
         <v>6280</v>
       </c>
     </row>
@@ -10243,34 +10195,34 @@
       <c r="A11" s="21">
         <v>6</v>
       </c>
-      <c r="B11" s="273" t="s">
+      <c r="B11" s="218" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="274">
+      <c r="C11" s="219">
         <v>14949</v>
       </c>
-      <c r="D11" s="274">
-        <v>0</v>
-      </c>
-      <c r="E11" s="274">
-        <v>0</v>
-      </c>
-      <c r="F11" s="274">
+      <c r="D11" s="219">
+        <v>0</v>
+      </c>
+      <c r="E11" s="219">
+        <v>0</v>
+      </c>
+      <c r="F11" s="219">
         <f t="shared" si="0"/>
         <v>14949</v>
       </c>
-      <c r="G11" s="275">
+      <c r="G11" s="220">
         <v>0.15</v>
       </c>
-      <c r="H11" s="274">
+      <c r="H11" s="219">
         <f t="shared" si="1"/>
         <v>2242</v>
       </c>
-      <c r="I11" s="274">
+      <c r="I11" s="219">
         <f t="shared" si="2"/>
         <v>12707</v>
       </c>
-      <c r="K11" s="272">
+      <c r="K11" s="217">
         <v>2638</v>
       </c>
     </row>
@@ -10278,34 +10230,34 @@
       <c r="A12" s="21">
         <v>7</v>
       </c>
-      <c r="B12" s="273" t="s">
+      <c r="B12" s="218" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="274">
+      <c r="C12" s="219">
         <v>28403</v>
       </c>
-      <c r="D12" s="274">
-        <v>0</v>
-      </c>
-      <c r="E12" s="274">
-        <v>0</v>
-      </c>
-      <c r="F12" s="274">
+      <c r="D12" s="219">
+        <v>0</v>
+      </c>
+      <c r="E12" s="219">
+        <v>0</v>
+      </c>
+      <c r="F12" s="219">
         <f t="shared" si="0"/>
         <v>28403</v>
       </c>
-      <c r="G12" s="275">
+      <c r="G12" s="220">
         <v>0.15</v>
       </c>
-      <c r="H12" s="274">
+      <c r="H12" s="219">
         <f t="shared" si="1"/>
         <v>4260</v>
       </c>
-      <c r="I12" s="274">
+      <c r="I12" s="219">
         <f t="shared" si="2"/>
         <v>24143</v>
       </c>
-      <c r="K12" s="272">
+      <c r="K12" s="217">
         <v>5012</v>
       </c>
     </row>
@@ -10313,111 +10265,112 @@
       <c r="A13" s="21">
         <v>8</v>
       </c>
-      <c r="B13" s="273" t="s">
+      <c r="B13" s="218" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="274">
+      <c r="C13" s="219">
         <v>346149</v>
       </c>
-      <c r="D13" s="274">
-        <v>0</v>
-      </c>
-      <c r="E13" s="274">
+      <c r="D13" s="219">
+        <v>0</v>
+      </c>
+      <c r="E13" s="219">
         <f>35800</f>
         <v>35800</v>
       </c>
-      <c r="F13" s="274">
+      <c r="F13" s="219">
         <f t="shared" si="0"/>
         <v>381949</v>
       </c>
-      <c r="G13" s="275">
+      <c r="G13" s="220">
         <v>0.1</v>
       </c>
-      <c r="H13" s="274">
+      <c r="H13" s="219">
         <f>ROUND(SUM(C13:D13,E13/2)*G13,)</f>
         <v>36405</v>
       </c>
-      <c r="I13" s="274">
+      <c r="I13" s="219">
         <f t="shared" si="2"/>
         <v>345544</v>
       </c>
-      <c r="K13" s="272">
+      <c r="K13" s="217">
         <v>32839.4</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="277">
+      <c r="A14" s="222">
         <v>9</v>
       </c>
-      <c r="B14" s="278" t="s">
+      <c r="B14" s="223" t="s">
         <v>470</v>
       </c>
-      <c r="C14" s="279">
-        <v>0</v>
-      </c>
-      <c r="D14" s="279">
-        <v>0</v>
-      </c>
-      <c r="E14" s="279">
+      <c r="C14" s="224">
+        <v>0</v>
+      </c>
+      <c r="D14" s="224">
+        <v>0</v>
+      </c>
+      <c r="E14" s="224">
         <f>168500+75000</f>
         <v>243500</v>
       </c>
-      <c r="F14" s="279">
+      <c r="F14" s="224">
         <f t="shared" ref="F14" si="3">C14+D14+E14</f>
         <v>243500</v>
       </c>
-      <c r="G14" s="280">
+      <c r="G14" s="225">
         <v>0.15</v>
       </c>
-      <c r="H14" s="279">
+      <c r="H14" s="224">
         <f>ROUND(SUM(C14:D14,E14/2)*G14,)</f>
         <v>18263</v>
       </c>
-      <c r="I14" s="279">
+      <c r="I14" s="224">
         <f t="shared" ref="I14" si="4">F14-H14</f>
         <v>225237</v>
       </c>
-      <c r="K14" s="272">
+      <c r="K14" s="217">
         <v>32839.4</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="22.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="253" t="s">
+      <c r="A15" s="303" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="254"/>
-      <c r="C15" s="281">
+      <c r="B15" s="304"/>
+      <c r="C15" s="226">
         <f>SUM(C6:C14)</f>
         <v>533313</v>
       </c>
-      <c r="D15" s="281">
+      <c r="D15" s="226">
         <f t="shared" ref="D15:F15" si="5">SUM(D6:D14)</f>
         <v>8950</v>
       </c>
-      <c r="E15" s="281">
+      <c r="E15" s="226">
         <f t="shared" si="5"/>
         <v>423302</v>
       </c>
-      <c r="F15" s="281">
+      <c r="F15" s="226">
         <f t="shared" si="5"/>
         <v>965565</v>
       </c>
-      <c r="G15" s="281"/>
-      <c r="H15" s="281">
+      <c r="G15" s="226"/>
+      <c r="H15" s="226">
         <f t="shared" ref="H15" si="6">SUM(H6:H14)</f>
         <v>100773</v>
       </c>
-      <c r="I15" s="282">
+      <c r="I15" s="227">
         <f t="shared" ref="I15" si="7">SUM(I6:I14)</f>
         <v>864792</v>
       </c>
-      <c r="K15" s="276">
+      <c r="K15" s="221">
         <f>SUM(K6:K13)</f>
         <v>70170.399999999994</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:I2"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C4:F4"/>
@@ -10425,7 +10378,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:I2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.51181102362204722" bottom="0.51181102362204722" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -10441,7 +10393,7 @@
     <col min="1" max="1" width="6.88671875" style="108" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="108" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="76.6640625" style="108" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.77734375" style="272" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" style="217" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="108"/>
     <col min="6" max="6" width="5.6640625" style="108" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.6640625" style="108" customWidth="1"/>
@@ -10450,53 +10402,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="287" t="str">
+      <c r="A1" s="316" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="288"/>
-      <c r="C1" s="288"/>
-      <c r="D1" s="289"/>
+      <c r="B1" s="317"/>
+      <c r="C1" s="317"/>
+      <c r="D1" s="318"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="290"/>
-      <c r="B2" s="262"/>
-      <c r="C2" s="262"/>
-      <c r="D2" s="291"/>
+      <c r="A2" s="319"/>
+      <c r="B2" s="320"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="321"/>
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="261" t="s">
+      <c r="A3" s="308" t="s">
         <v>473</v>
       </c>
-      <c r="B3" s="261"/>
-      <c r="C3" s="261"/>
-      <c r="D3" s="261"/>
+      <c r="B3" s="308"/>
+      <c r="C3" s="308"/>
+      <c r="D3" s="308"/>
     </row>
     <row r="4" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="286" t="s">
+      <c r="A4" s="231" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="286" t="s">
+      <c r="B4" s="231" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="286" t="s">
+      <c r="C4" s="231" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="251" t="s">
+      <c r="D4" s="205" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="268" t="s">
+      <c r="A5" s="213" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="268">
+      <c r="B5" s="213">
         <v>702</v>
       </c>
-      <c r="C5" s="285" t="s">
+      <c r="C5" s="230" t="s">
         <v>494</v>
       </c>
-      <c r="D5" s="270">
+      <c r="D5" s="215">
         <v>11800</v>
       </c>
     </row>
@@ -10507,10 +10459,10 @@
       <c r="B6" s="21">
         <v>1701</v>
       </c>
-      <c r="C6" s="283" t="s">
+      <c r="C6" s="228" t="s">
         <v>474</v>
       </c>
-      <c r="D6" s="274">
+      <c r="D6" s="219">
         <v>2950</v>
       </c>
     </row>
@@ -10521,10 +10473,10 @@
       <c r="B7" s="21">
         <v>2001</v>
       </c>
-      <c r="C7" s="283" t="s">
+      <c r="C7" s="228" t="s">
         <v>475</v>
       </c>
-      <c r="D7" s="274">
+      <c r="D7" s="219">
         <v>151487</v>
       </c>
     </row>
@@ -10535,10 +10487,10 @@
       <c r="B8" s="21">
         <v>3402</v>
       </c>
-      <c r="C8" s="283" t="s">
+      <c r="C8" s="228" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="274">
+      <c r="D8" s="219">
         <v>61155</v>
       </c>
     </row>
@@ -10549,10 +10501,10 @@
       <c r="B9" s="21">
         <v>1102</v>
       </c>
-      <c r="C9" s="283" t="s">
+      <c r="C9" s="228" t="s">
         <v>476</v>
       </c>
-      <c r="D9" s="274">
+      <c r="D9" s="219">
         <v>1025</v>
       </c>
     </row>
@@ -10563,10 +10515,10 @@
       <c r="B10" s="21">
         <v>1302</v>
       </c>
-      <c r="C10" s="283" t="s">
+      <c r="C10" s="228" t="s">
         <v>477</v>
       </c>
-      <c r="D10" s="274">
+      <c r="D10" s="219">
         <v>45</v>
       </c>
     </row>
@@ -10577,10 +10529,10 @@
       <c r="B11" s="21">
         <v>2001</v>
       </c>
-      <c r="C11" s="283" t="s">
+      <c r="C11" s="228" t="s">
         <v>328</v>
       </c>
-      <c r="D11" s="274">
+      <c r="D11" s="219">
         <v>8075</v>
       </c>
     </row>
@@ -10591,34 +10543,34 @@
       <c r="B12" s="21">
         <v>2701</v>
       </c>
-      <c r="C12" s="283" t="s">
+      <c r="C12" s="228" t="s">
         <v>478</v>
       </c>
-      <c r="D12" s="274">
+      <c r="D12" s="219">
         <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="277" t="s">
+      <c r="A13" s="222" t="s">
         <v>327</v>
       </c>
-      <c r="B13" s="277">
+      <c r="B13" s="222">
         <v>3402</v>
       </c>
-      <c r="C13" s="295" t="s">
+      <c r="C13" s="234" t="s">
         <v>336</v>
       </c>
-      <c r="D13" s="279">
+      <c r="D13" s="224">
         <v>8188</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="296"/>
-      <c r="B14" s="294"/>
-      <c r="C14" s="294" t="s">
+      <c r="A14" s="235"/>
+      <c r="B14" s="207"/>
+      <c r="C14" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="297">
+      <c r="D14" s="236">
         <f>SUM(D5:D13)</f>
         <v>245014</v>
       </c>
@@ -10626,13 +10578,13 @@
     <row r="15" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="66"/>
       <c r="C15" s="66"/>
-      <c r="D15" s="284"/>
+      <c r="D15" s="229"/>
     </row>
     <row r="16" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="165"/>
-      <c r="B16" s="165"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
+      <c r="A16" s="315"/>
+      <c r="B16" s="315"/>
+      <c r="C16" s="315"/>
+      <c r="D16" s="315"/>
     </row>
     <row r="17" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66"/>
@@ -10641,38 +10593,38 @@
       <c r="D17" s="62"/>
     </row>
     <row r="18" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="166" t="s">
+      <c r="A18" s="302" t="s">
         <v>479</v>
       </c>
-      <c r="B18" s="166"/>
-      <c r="C18" s="166"/>
-      <c r="D18" s="166"/>
+      <c r="B18" s="302"/>
+      <c r="C18" s="302"/>
+      <c r="D18" s="302"/>
     </row>
     <row r="19" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="286" t="s">
+      <c r="A19" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="286" t="s">
+      <c r="B19" s="231" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="286" t="s">
+      <c r="C19" s="231" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="251" t="s">
+      <c r="D19" s="205" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="268">
+      <c r="A20" s="213">
         <v>1</v>
       </c>
-      <c r="B20" s="268">
+      <c r="B20" s="213">
         <v>402</v>
       </c>
-      <c r="C20" s="269" t="s">
+      <c r="C20" s="214" t="s">
         <v>343</v>
       </c>
-      <c r="D20" s="270">
+      <c r="D20" s="215">
         <f>85500</f>
         <v>85500</v>
       </c>
@@ -10684,10 +10636,10 @@
       <c r="B21" s="21">
         <v>2402</v>
       </c>
-      <c r="C21" s="273" t="s">
+      <c r="C21" s="218" t="s">
         <v>480</v>
       </c>
-      <c r="D21" s="274">
+      <c r="D21" s="219">
         <v>2950</v>
       </c>
     </row>
@@ -10698,34 +10650,34 @@
       <c r="B22" s="21">
         <v>2701</v>
       </c>
-      <c r="C22" s="273" t="s">
+      <c r="C22" s="218" t="s">
         <v>478</v>
       </c>
-      <c r="D22" s="274">
+      <c r="D22" s="219">
         <v>11800</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="277">
+      <c r="A23" s="222">
         <v>4</v>
       </c>
-      <c r="B23" s="277" t="s">
+      <c r="B23" s="222" t="s">
         <v>344</v>
       </c>
-      <c r="C23" s="278" t="s">
+      <c r="C23" s="223" t="s">
         <v>343</v>
       </c>
-      <c r="D23" s="279">
+      <c r="D23" s="224">
         <v>11931</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="292"/>
-      <c r="B24" s="293"/>
-      <c r="C24" s="294" t="s">
+      <c r="A24" s="232"/>
+      <c r="B24" s="233"/>
+      <c r="C24" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="282">
+      <c r="D24" s="227">
         <f>SUM(D20:D23)</f>
         <v>112181</v>
       </c>
@@ -10759,53 +10711,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="287" t="str">
+      <c r="A1" s="316" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="288"/>
-      <c r="C1" s="288"/>
-      <c r="D1" s="289"/>
+      <c r="B1" s="317"/>
+      <c r="C1" s="317"/>
+      <c r="D1" s="318"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="290"/>
-      <c r="B2" s="262"/>
-      <c r="C2" s="262"/>
-      <c r="D2" s="291"/>
+      <c r="A2" s="319"/>
+      <c r="B2" s="320"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="321"/>
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="328" t="s">
+      <c r="A3" s="324" t="s">
         <v>223</v>
       </c>
-      <c r="B3" s="329"/>
-      <c r="C3" s="329"/>
-      <c r="D3" s="330"/>
+      <c r="B3" s="325"/>
+      <c r="C3" s="325"/>
+      <c r="D3" s="326"/>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="322" t="s">
+      <c r="A4" s="257" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="322" t="s">
+      <c r="B4" s="257" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="323" t="s">
+      <c r="C4" s="182" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="324" t="s">
+      <c r="D4" s="258" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="264">
+      <c r="A5" s="211">
         <v>2</v>
       </c>
-      <c r="B5" s="319">
+      <c r="B5" s="254">
         <v>14071</v>
       </c>
-      <c r="C5" s="320" t="s">
+      <c r="C5" s="255" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="321">
+      <c r="D5" s="256">
         <f>-Workings!D37</f>
         <v>6821</v>
       </c>
@@ -10899,69 +10851,69 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="315">
+      <c r="A12" s="250">
         <v>9</v>
       </c>
-      <c r="B12" s="316">
+      <c r="B12" s="251">
         <v>10500</v>
       </c>
-      <c r="C12" s="317" t="s">
+      <c r="C12" s="252" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="308">
+      <c r="D12" s="244">
         <f>-Workings!D66</f>
         <v>10500</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="304"/>
-      <c r="B13" s="318">
+      <c r="A13" s="240"/>
+      <c r="B13" s="253">
         <f>SUM(B5:B12)</f>
         <v>107878</v>
       </c>
-      <c r="C13" s="311" t="s">
+      <c r="C13" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="312">
+      <c r="D13" s="247">
         <f>SUM(D5:D12)</f>
         <v>144040</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="300" t="s">
+      <c r="A15" s="322" t="s">
         <v>378</v>
       </c>
-      <c r="B15" s="298"/>
-      <c r="C15" s="298"/>
-      <c r="D15" s="298"/>
+      <c r="B15" s="323"/>
+      <c r="C15" s="323"/>
+      <c r="D15" s="323"/>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="322" t="s">
+      <c r="A16" s="257" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="322" t="str">
+      <c r="B16" s="257" t="str">
         <f>B4</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C16" s="323" t="s">
+      <c r="C16" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="323" t="str">
+      <c r="D16" s="182" t="str">
         <f>D4</f>
         <v>FY 2025-26</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="325">
+      <c r="A17" s="259">
         <v>1</v>
       </c>
-      <c r="B17" s="326">
+      <c r="B17" s="260">
         <v>0</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>481</v>
       </c>
-      <c r="D17" s="327">
+      <c r="D17" s="261">
         <v>1860</v>
       </c>
     </row>
@@ -11148,29 +11100,29 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="301">
+      <c r="A31" s="237">
         <v>15</v>
       </c>
-      <c r="B31" s="302">
+      <c r="B31" s="238">
         <v>30680</v>
       </c>
       <c r="C31" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="303">
+      <c r="D31" s="239">
         <v>33660</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="304"/>
-      <c r="B32" s="305">
+      <c r="A32" s="240"/>
+      <c r="B32" s="241">
         <f>SUM(B17:B31)</f>
         <v>507786</v>
       </c>
-      <c r="C32" s="306" t="s">
+      <c r="C32" s="242" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="307">
+      <c r="D32" s="243">
         <f>SUM(D17:D31)</f>
         <v>299406</v>
       </c>
@@ -11181,32 +11133,32 @@
       <c r="B33"/>
     </row>
     <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="322" t="s">
+      <c r="A34" s="257" t="s">
         <v>163</v>
       </c>
-      <c r="B34" s="322" t="str">
+      <c r="B34" s="257" t="str">
         <f>B4</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C34" s="323" t="s">
+      <c r="C34" s="182" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="323" t="str">
+      <c r="D34" s="182" t="str">
         <f>D4</f>
         <v>FY 2025-26</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="325">
+      <c r="A35" s="259">
         <v>1</v>
       </c>
-      <c r="B35" s="326">
+      <c r="B35" s="260">
         <v>4879</v>
       </c>
       <c r="C35" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="321">
+      <c r="D35" s="256">
         <f>4816</f>
         <v>4816</v>
       </c>
@@ -11241,58 +11193,58 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="301">
+      <c r="A38" s="237">
         <v>4</v>
       </c>
-      <c r="B38" s="302">
+      <c r="B38" s="238">
         <v>80000</v>
       </c>
       <c r="C38" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="D38" s="308">
+      <c r="D38" s="244">
         <f>Workings!D83</f>
         <v>112630</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="304"/>
-      <c r="B39" s="310">
+      <c r="A39" s="240"/>
+      <c r="B39" s="245">
         <f>SUM(B35:B38)</f>
         <v>114401</v>
       </c>
-      <c r="C39" s="311" t="s">
+      <c r="C39" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="312">
+      <c r="D39" s="247">
         <f>SUM(D35:D38)</f>
         <v>173317</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="309"/>
-      <c r="B40" s="309"/>
-      <c r="C40" s="309"/>
+      <c r="A40" s="186"/>
+      <c r="B40" s="186"/>
+      <c r="C40" s="186"/>
       <c r="D40" s="17"/>
     </row>
     <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="322" t="s">
+      <c r="A41" s="257" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="322" t="str">
+      <c r="B41" s="257" t="str">
         <f>B4</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C41" s="323" t="s">
+      <c r="C41" s="182" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="323" t="str">
+      <c r="D41" s="182" t="str">
         <f>D4</f>
         <v>FY 2025-26</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="325">
+      <c r="A42" s="259">
         <v>1</v>
       </c>
       <c r="B42" s="149">
@@ -11349,7 +11301,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="301">
+      <c r="A46" s="237">
         <v>5</v>
       </c>
       <c r="B46" s="147">
@@ -11363,15 +11315,15 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="304"/>
-      <c r="B47" s="310">
+      <c r="A47" s="240"/>
+      <c r="B47" s="245">
         <f>SUM(B42:B46)</f>
         <v>58730</v>
       </c>
-      <c r="C47" s="313" t="s">
+      <c r="C47" s="248" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="314">
+      <c r="D47" s="249">
         <f>SUM(D42:D46)</f>
         <v>126019</v>
       </c>
@@ -11381,26 +11333,26 @@
       <c r="B48"/>
     </row>
     <row r="49" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="322" t="s">
+      <c r="A49" s="257" t="s">
         <v>163</v>
       </c>
-      <c r="B49" s="322" t="str">
+      <c r="B49" s="257" t="str">
         <f>B4</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C49" s="323" t="s">
+      <c r="C49" s="182" t="s">
         <v>329</v>
       </c>
-      <c r="D49" s="323" t="str">
+      <c r="D49" s="182" t="str">
         <f>D4</f>
         <v>FY 2025-26</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="264">
+      <c r="A50" s="211">
         <v>1</v>
       </c>
-      <c r="B50" s="326">
+      <c r="B50" s="260">
         <v>14800</v>
       </c>
       <c r="C50" s="41" t="s">
@@ -11439,10 +11391,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="315">
+      <c r="A53" s="250">
         <v>4</v>
       </c>
-      <c r="B53" s="302">
+      <c r="B53" s="238">
         <v>0</v>
       </c>
       <c r="C53" s="44" t="s">
@@ -11453,15 +11405,15 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="304"/>
-      <c r="B54" s="310">
+      <c r="A54" s="240"/>
+      <c r="B54" s="245">
         <f>SUM(B49:B53)</f>
         <v>20433</v>
       </c>
-      <c r="C54" s="313" t="s">
+      <c r="C54" s="248" t="s">
         <v>330</v>
       </c>
-      <c r="D54" s="314">
+      <c r="D54" s="249">
         <f>SUM(D49:D53)</f>
         <v>35000</v>
       </c>
@@ -11495,36 +11447,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="336" t="str">
+      <c r="A1" s="327" t="str">
         <f>+'Sch 3&amp;7'!A1:D1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="337"/>
-      <c r="C1" s="337"/>
-      <c r="D1" s="337"/>
-      <c r="E1" s="338"/>
+      <c r="B1" s="328"/>
+      <c r="C1" s="328"/>
+      <c r="D1" s="328"/>
+      <c r="E1" s="329"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="330" t="s">
         <v>383</v>
       </c>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="173"/>
+      <c r="B2" s="331"/>
+      <c r="C2" s="331"/>
+      <c r="D2" s="331"/>
+      <c r="E2" s="332"/>
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="323" t="s">
+      <c r="A3" s="182" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="323" t="s">
+      <c r="B3" s="182" t="s">
         <v>281</v>
       </c>
-      <c r="C3" s="323" t="s">
+      <c r="C3" s="182" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="323"/>
-      <c r="E3" s="323" t="s">
+      <c r="D3" s="182"/>
+      <c r="E3" s="182" t="s">
         <v>375</v>
       </c>
     </row>
@@ -11592,7 +11544,7 @@
       </c>
       <c r="D8" s="38">
         <f>PL!D45</f>
-        <v>182865</v>
+        <v>134513</v>
       </c>
       <c r="E8" s="51"/>
     </row>
@@ -11611,11 +11563,11 @@
       </c>
       <c r="E9" s="51">
         <f>SUM(D5:D9)</f>
-        <v>1024851</v>
+        <v>976499</v>
       </c>
       <c r="G9" s="24">
         <f>E9-'Sch 1'!M28</f>
-        <v>-128719</v>
+        <v>-177071</v>
       </c>
       <c r="H9" t="s">
         <v>355</v>
@@ -11744,8 +11696,7 @@
         <v>212</v>
       </c>
       <c r="D19" s="47">
-        <f>PL!C19+'Sch 8 &amp; 9'!D25+'Sch 8 &amp; 9'!D28</f>
-        <v>-1063146</v>
+        <v>-869739</v>
       </c>
       <c r="E19" s="53"/>
     </row>
@@ -11764,11 +11715,11 @@
       </c>
       <c r="E20" s="55">
         <f>SUM(D17:D20)</f>
-        <v>1400379.0899999999</v>
+        <v>1593786.0899999999</v>
       </c>
       <c r="G20" s="24">
         <f>E20-'Sch 1'!M19</f>
-        <v>-458183.91000000015</v>
+        <v>-264776.91000000015</v>
       </c>
       <c r="H20" t="s">
         <v>355</v>
@@ -11922,24 +11873,24 @@
       <c r="E31" s="58"/>
     </row>
     <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="331"/>
-      <c r="B32" s="332">
+      <c r="A32" s="262"/>
+      <c r="B32" s="263">
         <f>SUM(B4:B31)</f>
         <v>3977417.09</v>
       </c>
-      <c r="C32" s="333" t="s">
+      <c r="C32" s="264" t="s">
         <v>173</v>
       </c>
-      <c r="D32" s="334"/>
-      <c r="E32" s="335">
+      <c r="D32" s="265"/>
+      <c r="E32" s="266">
         <f>SUM(E4:E31)</f>
-        <v>4575563.09</v>
+        <v>4720618.09</v>
       </c>
     </row>
     <row r="34" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E34" s="135">
         <f>E32-D8</f>
-        <v>4392698.09</v>
+        <v>4586105.09</v>
       </c>
     </row>
   </sheetData>
@@ -11966,56 +11917,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="284" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="200"/>
+      <c r="B1" s="285"/>
+      <c r="C1" s="285"/>
+      <c r="D1" s="286"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="177"/>
-      <c r="B2" s="210"/>
-      <c r="C2" s="210"/>
+      <c r="A2" s="161"/>
       <c r="D2" s="27"/>
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="300" t="s">
+      <c r="A3" s="322" t="s">
         <v>386</v>
       </c>
-      <c r="B3" s="298"/>
-      <c r="C3" s="298"/>
-      <c r="D3" s="299"/>
+      <c r="B3" s="323"/>
+      <c r="C3" s="323"/>
+      <c r="D3" s="333"/>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="322" t="s">
+      <c r="A4" s="257" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="322" t="str">
+      <c r="B4" s="257" t="str">
         <f>'Sch 4,6'!B4</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C4" s="323" t="s">
+      <c r="C4" s="182" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="341" t="str">
+      <c r="D4" s="269" t="str">
         <f>'Sch 4,6'!D4</f>
         <v>FY 2025-26</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="325">
+      <c r="A5" s="259">
         <v>1</v>
       </c>
-      <c r="B5" s="339">
+      <c r="B5" s="267">
         <f>11341+3875</f>
         <v>15216</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="340">
+      <c r="D5" s="268">
         <f>11562</f>
         <v>11562</v>
       </c>
@@ -12171,55 +12120,55 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="345"/>
-      <c r="B16" s="346">
+      <c r="A16" s="273"/>
+      <c r="B16" s="274">
         <f>SUM(B5:B15)</f>
         <v>420243</v>
       </c>
-      <c r="C16" s="323" t="s">
+      <c r="C16" s="182" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="346">
+      <c r="D16" s="274">
         <f>SUM(D5:D15)</f>
         <v>424898</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="170" t="s">
+      <c r="A18" s="334" t="s">
         <v>385</v>
       </c>
-      <c r="B18" s="164"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="164"/>
+      <c r="B18" s="275"/>
+      <c r="C18" s="275"/>
+      <c r="D18" s="275"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="322" t="s">
+      <c r="A19" s="257" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="322" t="str">
+      <c r="B19" s="257" t="str">
         <f>B4</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C19" s="323" t="s">
+      <c r="C19" s="182" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="323" t="str">
+      <c r="D19" s="182" t="str">
         <f>D4</f>
         <v>FY 2025-26</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="325">
+      <c r="A20" s="259">
         <v>1</v>
       </c>
-      <c r="B20" s="339">
+      <c r="B20" s="267">
         <v>6444</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="340">
+      <c r="D20" s="268">
         <f>Workings!D16</f>
         <v>5011</v>
       </c>
@@ -12286,8 +12235,7 @@
         <v>213</v>
       </c>
       <c r="D25" s="124">
-        <f>-D24</f>
-        <v>-132000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -12322,8 +12270,7 @@
         <v>213</v>
       </c>
       <c r="D28" s="124">
-        <f>-D27</f>
-        <v>-232407</v>
+        <v>-171000</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -12365,17 +12312,17 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="345"/>
-      <c r="B32" s="346">
+      <c r="A32" s="273"/>
+      <c r="B32" s="274">
         <f>SUM(B20:B31)</f>
         <v>103874</v>
       </c>
-      <c r="C32" s="323" t="s">
+      <c r="C32" s="182" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="346">
+      <c r="D32" s="274">
         <f>SUM(D20:D31)</f>
-        <v>107821</v>
+        <v>301228</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12383,17 +12330,17 @@
       <c r="D33" s="125"/>
     </row>
     <row r="34" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="342"/>
-      <c r="B34" s="343">
+      <c r="A34" s="270"/>
+      <c r="B34" s="271">
         <f>B16+B32</f>
         <v>524117</v>
       </c>
-      <c r="C34" s="333" t="s">
+      <c r="C34" s="264" t="s">
         <v>228</v>
       </c>
-      <c r="D34" s="344">
+      <c r="D34" s="272">
         <f>D16+D32</f>
-        <v>532719</v>
+        <v>726126</v>
       </c>
     </row>
   </sheetData>
@@ -12436,29 +12383,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B1" s="163" t="str">
+      <c r="B1" s="276" t="str">
         <f>BS!A1</f>
         <v>JEEVAN HEIGHTS  CO-OPERATIVE HOUSING SOCIETY LTD</v>
       </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="163"/>
-      <c r="H1" s="163"/>
-      <c r="I1" s="163"/>
-      <c r="J1" s="163"/>
-      <c r="K1" s="163"/>
-      <c r="L1" s="163"/>
+      <c r="C1" s="276"/>
+      <c r="D1" s="276"/>
+      <c r="E1" s="276"/>
+      <c r="F1" s="276"/>
+      <c r="G1" s="276"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="276"/>
+      <c r="J1" s="276"/>
+      <c r="K1" s="276"/>
+      <c r="L1" s="276"/>
       <c r="M1" s="75"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="276" t="s">
         <v>377</v>
       </c>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
+      <c r="B3" s="276"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
       <c r="F3" s="13" t="s">
         <v>46</v>
       </c>
@@ -12481,13 +12428,13 @@
         <v>51</v>
       </c>
       <c r="M3" s="66"/>
-      <c r="O3" s="174" t="s">
+      <c r="O3" s="277" t="s">
         <v>293</v>
       </c>
-      <c r="P3" s="175"/>
-      <c r="Q3" s="175"/>
-      <c r="R3" s="175"/>
-      <c r="S3" s="176"/>
+      <c r="P3" s="278"/>
+      <c r="Q3" s="278"/>
+      <c r="R3" s="278"/>
+      <c r="S3" s="279"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F4" s="16">
@@ -12535,10 +12482,10 @@
       <c r="A5" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="164" t="s">
+      <c r="B5" s="275" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="164"/>
+      <c r="C5" s="275"/>
       <c r="D5" s="17" t="s">
         <v>375</v>
       </c>
@@ -12899,12 +12846,12 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="163" t="s">
+      <c r="A18" s="276" t="s">
         <v>376</v>
       </c>
-      <c r="B18" s="163"/>
-      <c r="C18" s="163"/>
-      <c r="D18" s="163"/>
+      <c r="B18" s="276"/>
+      <c r="C18" s="276"/>
+      <c r="D18" s="276"/>
       <c r="N18" s="16">
         <v>14</v>
       </c>
@@ -12945,10 +12892,10 @@
         <f>A5</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="275" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="164"/>
+      <c r="C20" s="275"/>
       <c r="D20" s="154" t="str">
         <f>D5</f>
         <v>FY 2025-26</v>
@@ -13062,22 +13009,22 @@
     </row>
     <row r="31" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="163" t="s">
+      <c r="A32" s="276" t="s">
         <v>493</v>
       </c>
-      <c r="B32" s="163"/>
-      <c r="C32" s="163"/>
-      <c r="D32" s="163"/>
+      <c r="B32" s="276"/>
+      <c r="C32" s="276"/>
+      <c r="D32" s="276"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="154" t="str">
         <f>A5</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="B34" s="164" t="s">
+      <c r="B34" s="275" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="164"/>
+      <c r="C34" s="275"/>
       <c r="D34" s="154" t="str">
         <f>D5</f>
         <v>FY 2025-26</v>
